--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -9058,7 +9058,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>【社長確認】写真(T0006)が横倒しで保存されている(EXIF回転なし)。動画化前に反時計回り90°回転が必要。問いの内容はmanual 04_交配舎と一致｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
+          <t>【解決済: 切り出し時に反時計回り90°で正立させた(rotate=-90)】 (元)写真(T0006)が横倒しで保存されている(EXIF回転なし)。動画化前に反時計回り90°回転が必要。問いの内容はmanual 04_交配舎と一致｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>【社長確認】素材台帳では『死亡子豚_多数』。写真の子豚が寝ている（寒い）のか死亡しているのか確認が必要。死亡なら drop / 素材台帳の命名は『死亡子豚_多数』。寝ているのか死亡しているのか監修で確認が必要</t>
+          <t>【解決済 09-24 リーダー確認: 原寸で生きた離乳子豚が重なって寝ている(頭を上げた個体・開眼)=台帳名の誤り】 (元)素材台帳では『死亡子豚_多数』。写真の子豚が寝ている（寒い）のか死亡しているのか確認が必要。死亡なら drop / 素材台帳の命名は『死亡子豚_多数』。寝ているのか死亡しているのか監修で確認が必要</t>
         </is>
       </c>
     </row>

--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK305"/>
+  <dimension ref="A1:AL305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -617,6 +617,11 @@
           <t>check_note</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -748,6 +753,16 @@
           <t>Mengganti pakaian</t>
         </is>
       </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>q01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -879,6 +894,16 @@
           <t>Celemek</t>
         </is>
       </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>q02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1010,6 +1035,16 @@
           <t>Membuang obat</t>
         </is>
       </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>q03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1141,6 +1176,16 @@
           <t>Mengisi botol dengan air</t>
         </is>
       </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>q04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1272,6 +1317,16 @@
           <t>Memberi makan</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>q05</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1403,6 +1458,16 @@
           <t>Untuk mendisinfeksi luka</t>
         </is>
       </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>q06</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1534,6 +1599,16 @@
           <t>Anak babi yang kecil</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>q07</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1665,6 +1740,16 @@
           <t>Di kantor, menulis catatan</t>
         </is>
       </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>q08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1796,6 +1881,16 @@
           <t>Mengikat anak babi dengan tali</t>
         </is>
       </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>q09</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1927,6 +2022,16 @@
           <t>Menyuntik babi</t>
         </is>
       </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>q10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2058,6 +2163,16 @@
           <t>Hanya celana kerja</t>
         </is>
       </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>q11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2189,6 +2304,16 @@
           <t>Untuk mengangkut babi</t>
         </is>
       </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>q12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2320,6 +2445,16 @@
           <t>Mendisinfeksi luka di leher</t>
         </is>
       </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2451,6 +2586,16 @@
           <t>Anak babi sakit. Akan disuntik</t>
         </is>
       </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>q14</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2582,6 +2727,16 @@
           <t>Ruang pembuatan pakan</t>
         </is>
       </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>q15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2713,6 +2868,16 @@
           <t>Anak babi baru lahir bersama induk</t>
         </is>
       </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>q16</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2844,6 +3009,16 @@
           <t>Tangki penyimpan gas</t>
         </is>
       </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>q17</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2975,6 +3150,16 @@
           <t>Di dalam mobil, menghitung obat</t>
         </is>
       </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>q18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3106,6 +3291,16 @@
           <t>Agar terlihat rapi</t>
         </is>
       </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>q19</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3237,6 +3432,16 @@
           <t>Membagikan pakan</t>
         </is>
       </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>q20</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3368,6 +3573,16 @@
           <t>Gudang pakan</t>
         </is>
       </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>q21</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3499,6 +3714,16 @@
           <t>Tiap ekor diikat di luar</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>q22</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3630,6 +3855,16 @@
           <t>Merendam alat suntik dalam air</t>
         </is>
       </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>q23</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3761,6 +3996,16 @@
           <t>Berjalan di atas pagar</t>
         </is>
       </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>q24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3892,6 +4137,16 @@
           <t>Tidak memakai</t>
         </is>
       </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>q25</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4023,6 +4278,16 @@
           <t>Memuat babi</t>
         </is>
       </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>q26</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4154,6 +4419,16 @@
           <t>Perut</t>
         </is>
       </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>q06</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4285,6 +4560,16 @@
           <t>Babi yang tidur</t>
         </is>
       </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>q12</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4416,6 +4701,16 @@
           <t>Harganya</t>
         </is>
       </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>q01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4547,6 +4842,16 @@
           <t>Dibuang</t>
         </is>
       </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>q13</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4703,6 +5008,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4859,6 +5169,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>M013</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5015,6 +5330,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>M034</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5171,6 +5491,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>I013</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5327,6 +5652,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>M019</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5483,6 +5813,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>M041</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5639,6 +5974,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>M003</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5795,6 +6135,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>M007</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5951,6 +6296,11 @@
           <t>【社長確認】種雄番号欄の3つの数字＝3回の授精ごとの雄番号という解釈は帳面から推定したもの（manualは2回交配推奨・3回は状況次第）。行によっては4つ目の小さい数字もある。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>M021</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6107,6 +6457,11 @@
           <t>【社長確認】「pm」＝午後の種付けは一般的な略記からの推定でmanualに明記なし（manualは授精日時の記録を求めるのみ）。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>M034</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6263,6 +6618,11 @@
           <t>根拠箇所を実在する節に修正（05_妊娠舎に該当節なし→04_交配舎 ミス4「記録を後でまとめて書く／その場で記録する」+05 よくある失敗）。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>M017</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6419,6 +6779,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>I009</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6575,6 +6940,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>I015</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6731,6 +7101,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>I019</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6887,6 +7262,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>M034</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7043,6 +7423,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>M029</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7199,6 +7584,11 @@
           <t>I005はピント甘く傾きあり→同内容で鮮明なM009に差し替え（妊娠確認1回の欄に○△の記号あり）。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>M009</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7355,6 +7745,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>M023</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7511,6 +7906,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>I001</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7667,6 +8067,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>M005</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7823,6 +8228,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>M025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7979,6 +8389,11 @@
           <t>rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>M011</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8135,6 +8550,11 @@
           <t>【社長確認】manualは2回交配推奨だが、帳面は1行に雄番号が3つ（3回授精）の行が大半＝睦沢は3回の可能性。現場ルールと矛盾するなら出題しない方がよい。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>M041</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8291,6 +8711,11 @@
           <t>100頭中97頭→97%は単純計算のため上級→中級に変更（定義はmanual 11章3-1に一致）。id「angka kebuntingan」→「tingkat kebuntingan」。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>M033</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8447,6 +8872,11 @@
           <t>【社長確認】manualの大腸菌ワクチン例（分娩予定2〜4週前）に沿った計算問だが、睦沢の注射カレンダーは交配日基準。現場の実プログラムと食い違うなら差し替え。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>M009</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8598,6 +9028,11 @@
           <t>T0243</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>T0243</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8749,6 +9184,11 @@
           <t>T0243</t>
         </is>
       </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>T0243</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8905,6 +9345,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>T0012</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9061,6 +9506,11 @@
           <t>【解決済: 切り出し時に反時計回り90°で正立させた(rotate=-90)】 (元)写真(T0006)が横倒しで保存されている(EXIF回転なし)。動画化前に反時計回り90°回転が必要。問いの内容はmanual 04_交配舎と一致｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>T0006</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9217,6 +9667,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>T0200</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9373,6 +9828,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>T0200</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9529,6 +9989,11 @@
           <t>sceneを事実どおりに修正(便と断定しない)。問い自体は写真に依存しない知識問題でmanual 07/06と一致</t>
         </is>
       </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>T0114</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9680,6 +10145,11 @@
           <t>T0117</t>
         </is>
       </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>T0117</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9836,6 +10306,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>T0117</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9987,6 +10462,11 @@
           <t>T0107</t>
         </is>
       </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>T0107</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10143,6 +10623,11 @@
           <t>写真だけでは給水用かクーリング用の配管かは断定できない。どちらでも「水の出が悪くなる」は成り立つ</t>
         </is>
       </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>T0101</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10294,6 +10779,11 @@
           <t>T0092</t>
         </is>
       </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>T0092</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10445,6 +10935,11 @@
           <t>T0090</t>
         </is>
       </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>T0090</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10601,6 +11096,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>T0047</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10752,6 +11252,11 @@
           <t>T0392</t>
         </is>
       </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>T0392</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10908,6 +11413,11 @@
           <t>巣と断定はできない（枝の集まり）。「かもしれない」とした。監修で判断を</t>
         </is>
       </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>T0168</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11064,6 +11574,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>T0100</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11220,6 +11735,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>T0167</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11371,6 +11891,11 @@
           <t>T0167</t>
         </is>
       </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>T0167</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11527,6 +12052,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>T0171</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11683,6 +12213,11 @@
           <t>【QA】同じ場面の q94 の問題文（皮膚が紫色）がこの問いの答えを含む。同じ回に出ると答えが分かる（確率は約1%）</t>
         </is>
       </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>T0140</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11834,6 +12369,11 @@
           <t>T0140</t>
         </is>
       </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>T0140</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11990,6 +12530,11 @@
           <t>かたまりが何か（胎子・胎膜等）は写真で断定しない表現にした</t>
         </is>
       </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>T0141</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12141,6 +12686,11 @@
           <t>T0276</t>
         </is>
       </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>T0276</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12292,6 +12842,11 @@
           <t>T0160</t>
         </is>
       </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>T0160</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -12448,6 +13003,11 @@
           <t>【社長確認】傷がけんか由来かは写真で断定できない(こすれ・皮膚病の可能性)。manual 08は「皮膚の傷が多い=闘争や圧迫」｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 傷の原因は写真だけでは断定できないため「多い原因」として問うた / 【QA】同じ場面の q93 の答え（傷がたくさん）を問題文に含む。どちらか一方にするか検討</t>
         </is>
       </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>T0162</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12604,6 +13164,11 @@
           <t>【社長確認】カードの文字はスマホ画面では読めない(縦写真・小文字)ため問いは知識問題として成立させ、難易度を初級へ。カード様式は農場ごと(写真は高橋さん農場)なのでヒラノの様式と合うか確認 / カードの文字はスマホでは読めない前提(問いは文字を読まずに答えられる)。カード様式は農場ごとに異なる</t>
         </is>
       </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>T0098</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12760,6 +13325,11 @@
           <t>写真の人はスプレーを持っておらず尾の処置中に見える(スプレーの印は書き終わっている)ため、問いを「青い印は何か」に作り替え｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 人はスプレーではなく尾の処置中に見える。顔は写っていない</t>
         </is>
       </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>T0015</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12911,6 +13481,11 @@
           <t>T0616</t>
         </is>
       </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>T0616</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13067,6 +13642,11 @@
           <t>ひも状のもの=へその緒と判断。分娩中か分娩直後かは写真だけでは断定できないため『分娩』とした</t>
         </is>
       </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>T0569</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13218,6 +13798,11 @@
           <t>T0569</t>
         </is>
       </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>T0569</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13374,6 +13959,11 @@
           <t>写真は乳房のみ。問いは乳汁テストの知識</t>
         </is>
       </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>T0558</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13530,6 +14120,11 @@
           <t>【社長確認】床の黄色いものが子豚の下痢便で間違いないか（嘔吐物の可能性）。見て判断が要るため難易度を中級に変更｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 床の黄色いペースト状のものが下痢便か嘔吐物か写真だけでは断定できない</t>
         </is>
       </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>T0407</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13681,6 +14276,11 @@
           <t>T0407</t>
         </is>
       </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>T0407</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13837,6 +14437,11 @@
           <t>【解決済 09-24 リーダー確認: 原寸で生きた離乳子豚が重なって寝ている(頭を上げた個体・開眼)=台帳名の誤り】 (元)素材台帳では『死亡子豚_多数』。写真の子豚が寝ている（寒い）のか死亡しているのか確認が必要。死亡なら drop / 素材台帳の命名は『死亡子豚_多数』。寝ているのか死亡しているのか監修で確認が必要</t>
         </is>
       </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>T0463</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13993,6 +14598,11 @@
           <t>病名（ヘルニア）は選択肢に出していない</t>
         </is>
       </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>T0412</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14149,6 +14759,11 @@
           <t>写真の針は耳のうしろ〜首付近。既存q09（保定+注射）とは観点が異なる（部位）</t>
         </is>
       </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>T0451</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14305,6 +14920,11 @@
           <t>【社長確認】写真の豚は母豚(台帳『母豚_横臥』)で肥育カテゴリは不適。背中の病変がかみ傷と断定できないため正解を『傷やかさぶたがたくさんある』に変更・カテゴリを衛生・防疫へ / 写真の豚は母豚と思われ（台帳『母豚_横臥』）、傷がかみ傷かは断定できない / 【QA】同じ場面の q81 の問題文（かまれたような傷）がこの問いの答えを含む（同じ回に出る確率は約1%）</t>
         </is>
       </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>T0162</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14461,6 +15081,11 @@
           <t>病名は出していない。紫色の変色はかなりはっきり写っている / 【QA】同じ場面の q76 の答え（皮膚が赤紫色）を問題文に含む。どちらか一方にするか検討</t>
         </is>
       </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>T0140</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14612,6 +15237,11 @@
           <t>T0715</t>
         </is>
       </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>T0715</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14763,6 +15393,11 @@
           <t>T0715</t>
         </is>
       </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>T0715</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -14919,6 +15554,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>T0730</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -15070,6 +15710,11 @@
           <t>T0514</t>
         </is>
       </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>T0514</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -15226,6 +15871,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>T0177</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -15377,6 +16027,11 @@
           <t>T0644</t>
         </is>
       </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>T0177</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15528,6 +16183,11 @@
           <t>T0512</t>
         </is>
       </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>T0166</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -15679,6 +16339,11 @@
           <t>T0411</t>
         </is>
       </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>T0116</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -15830,6 +16495,11 @@
           <t>T0411</t>
         </is>
       </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>T0116</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -15981,6 +16651,11 @@
           <t>T0728</t>
         </is>
       </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>T0728</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -16132,6 +16807,11 @@
           <t>T0635</t>
         </is>
       </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>T0635</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -16283,6 +16963,11 @@
           <t>T0635</t>
         </is>
       </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>T0635</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -16439,6 +17124,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>T0540</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16590,6 +17280,11 @@
           <t>T0540</t>
         </is>
       </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>T0540</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16746,6 +17441,11 @@
           <t>掘った動物の種類は写真からは断定できないため『野生動物かもしれない』とした</t>
         </is>
       </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>T0534</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -16897,6 +17597,11 @@
           <t>T0547</t>
         </is>
       </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>T0547</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -17053,6 +17758,11 @@
           <t>【社長確認】白い粉が消石灰で間違いないか（台帳名は『豚舎_通路』）。id の『kapur tohor』は生石灰の意味なので『kapur mati』に修正 / 白い粉=消石灰と判断（素材名は『豚舎_通路』）。監修で確認してほしい</t>
         </is>
       </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>T0753</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -17209,6 +17919,11 @@
           <t>id の『kapur tohor』(生石灰)を『kapur mati』(消石灰)に修正</t>
         </is>
       </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>T0753</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -17365,6 +18080,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>T0754</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -17521,6 +18241,11 @@
           <t>カード上部に農場名（ヒラノ 那須農場）が小さく写る。個人情報なし</t>
         </is>
       </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>T1044</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -17672,6 +18397,11 @@
           <t>T1044</t>
         </is>
       </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>T1044</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -17828,6 +18558,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>T1040</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -17979,6 +18714,11 @@
           <t>T0959</t>
         </is>
       </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>T0959</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -18135,6 +18875,11 @@
           <t>針は20℃をわずかに超える位置。『約20℃』と表現</t>
         </is>
       </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>T0961</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -18291,6 +19036,11 @@
           <t>【社長確認】写真は離乳房が過密で、ランプ下の重なりを「寒いサイン」と読んでよいか(過密にも見える)。問い・根拠(12章 ランプの下で重なり合う=非常に寒い)は正しい</t>
         </is>
       </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>T1193</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -18442,6 +19192,11 @@
           <t>T0965</t>
         </is>
       </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>T0965</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -18593,6 +19348,11 @@
           <t>T0965</t>
         </is>
       </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>T0965</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18744,6 +19504,11 @@
           <t>T0986</t>
         </is>
       </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>T0986</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -18900,6 +19665,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>T0914</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -19056,6 +19826,11 @@
           <t>機器の操作パネル画面（スマホ画面ではない）</t>
         </is>
       </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>T1135</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -19207,6 +19982,11 @@
           <t>T0910</t>
         </is>
       </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>T0910</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -19358,6 +20138,11 @@
           <t>T1198</t>
         </is>
       </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>T1198</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -19514,6 +20299,11 @@
           <t>病名は問わない（色の異常に気づき報告する）</t>
         </is>
       </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>T1200</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -19670,6 +20460,11 @@
           <t>病名は問わない</t>
         </is>
       </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>T0990</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -19826,6 +20621,11 @@
           <t>虫は実物ではうすいピンク色で「白っぽい」は不正確。全言語で「細長いひものようなもの」に統一。スマホでも線として判別可(問いで存在を明示) / 寄生虫の種類名（病名）は出さない</t>
         </is>
       </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>T1137</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -19982,6 +20782,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t>T1001</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -20133,6 +20938,11 @@
           <t>T1185</t>
         </is>
       </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>T1185</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -20284,6 +21094,11 @@
           <t>T1185</t>
         </is>
       </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>T1185</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -20435,6 +21250,11 @@
           <t>T1184</t>
         </is>
       </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>T1184</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -20586,6 +21406,11 @@
           <t>T1184</t>
         </is>
       </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>T1184</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -20742,6 +21567,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>T1192</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -20893,6 +21723,11 @@
           <t>T0920</t>
         </is>
       </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>T0920</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21049,6 +21884,11 @@
           <t>箱の製品名が読める。薬の名前・用量は問わない</t>
         </is>
       </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>T1129</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21200,6 +22040,11 @@
           <t>T1129</t>
         </is>
       </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>T1129</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21351,6 +22196,11 @@
           <t>T1124</t>
         </is>
       </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>T1124</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21507,6 +22357,11 @@
           <t>【社長確認】青い箱の白い粉が本当に消石灰か(写真からは断定不可、問いは消石灰と断定している)。根拠(02章 水分がないと効果が弱い)は正しい / 白い粉が消石灰であることは manual 02 の同系写真『消石灰の踏込消毒コンテナ』に基づく</t>
         </is>
       </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>T0989</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21658,6 +22513,11 @@
           <t>T0992</t>
         </is>
       </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>T0992</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -21809,6 +22669,11 @@
           <t>T0992</t>
         </is>
       </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>T0992</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -21965,6 +22830,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>T0016</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22116,6 +22986,11 @@
           <t>T1194</t>
         </is>
       </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>T1194</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -22267,6 +23142,11 @@
           <t>T1174</t>
         </is>
       </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>T1174</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -22423,6 +23303,11 @@
           <t>網の拡大写真。何の網か分かりにくければ不採用可</t>
         </is>
       </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>T0932</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -22579,6 +23464,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 直腸脱か子宮脱か写真では断定しない。病名を出さず『触らず・すぐ呼ぶ』を問う。血が写るので刺激強め</t>
         </is>
       </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>T1106</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -22735,6 +23625,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 母豚の体に少量の血が写る</t>
         </is>
       </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>T1188</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -22891,6 +23786,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>T1188</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -23047,6 +23947,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>T0128@5</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -23203,6 +24108,11 @@
           <t>【社長確認】6〜10秒の映像では左の母豚の外陰部はピンク〜やや赤い程度で「赤く腫れている」と断定しにくい。発情サインの例として使ってよいか確認(元命名は「採血」)</t>
         </is>
       </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>T0131@6</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -23354,6 +24264,11 @@
           <t>T0131@6</t>
         </is>
       </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>T0131@6</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -23510,6 +24425,11 @@
           <t>作業者の顔が映る場面(0秒・27〜33秒付近)は避けた</t>
         </is>
       </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>T0132@4</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -23661,6 +24581,11 @@
           <t>T0132@35</t>
         </is>
       </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>T0132@35</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -23812,6 +24737,11 @@
           <t>T0132@35</t>
         </is>
       </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>T0132@35</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -23963,6 +24893,11 @@
           <t>T0132@35</t>
         </is>
       </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>T0132@35</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -24119,6 +25054,11 @@
           <t>「正しいやり方」を問う問題なので難易度を上級→中級に修正(内容は04_交配舎 5.清拭「上から下に拭く」と一致)</t>
         </is>
       </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>T0306@1</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -24275,6 +25215,11 @@
           <t>【社長確認】この恒温器が精液保管用インキュベーターか(上の「交配①②」ファイルからの推定)。違えばこの問は削除。tv2のT0652(同一ファイル)は「〜だとします」と仮定形で出題済み / 上に「交配①②」ファイルがあるため精液保管用インキュベーターと推定。実際の用途を監修で要確認（違えばこの素材の3問は削除）</t>
         </is>
       </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>T0134@3</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -24431,6 +25376,11 @@
           <t>流産か妊娠舎での早い分娩かは映像で断定できないため、問いでは病名・原因を出さない。どちらでも「すぐ報告・胎子保管」は同じ</t>
         </is>
       </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>T0149@2.5</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -24587,6 +25537,11 @@
           <t>流産か妊娠舎での早い分娩かは映像で断定できないため、問いでは病名・原因を出さない。どちらでも「すぐ報告・胎子保管」は同じ</t>
         </is>
       </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>T0149@2.5</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -24738,6 +25693,11 @@
           <t>T0151@3</t>
         </is>
       </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>T0151@3</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -24889,6 +25849,11 @@
           <t>T0075@0</t>
         </is>
       </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>T0075@0</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -25045,6 +26010,11 @@
           <t>【社長確認】黄色い丸皿(赤い回転パドル付き)が子豚の餌付け皿か。給水用の丸皿なら誤答「母豚の水飲み」と紛れるので削除が必要。子豚の体が茶色いのは問わない / 形状から子豚用の餌付け皿と判断。監修で確認。子豚の体が茶色い理由は不明なので問わない</t>
         </is>
       </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>T0078@2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -25196,6 +26166,11 @@
           <t>T0388@10</t>
         </is>
       </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>T0388@10</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -25347,6 +26322,11 @@
           <t>T0388@10</t>
         </is>
       </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>T0388@10</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -25498,6 +26478,11 @@
           <t>T0521@0.5</t>
         </is>
       </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>T0521@0.5</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -25649,6 +26634,11 @@
           <t>T0127@1</t>
         </is>
       </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>T0127@1</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -25805,6 +26795,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>T0127@1</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -25961,6 +26956,11 @@
           <t>ネズミは死んでいる。床の黒い粒はふんと判断(監修確認)</t>
         </is>
       </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>T0549@3</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -26112,6 +27112,11 @@
           <t>T0549@3</t>
         </is>
       </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>T0549@3</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -26263,6 +27268,11 @@
           <t>T0053@2</t>
         </is>
       </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>T0053@2</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -26414,6 +27424,11 @@
           <t>T0034@4.5</t>
         </is>
       </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>T0034@4.5</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -26565,6 +27580,11 @@
           <t>T0034@4.5</t>
         </is>
       </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>T0034@4.5</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -26721,6 +27741,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>T0138@5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -26872,6 +27897,11 @@
           <t>T0138@5</t>
         </is>
       </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>T0138@5</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -27028,6 +28058,11 @@
           <t>映像はシャッターのみ（知識問題）</t>
         </is>
       </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>T0138@5</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -27179,6 +28214,11 @@
           <t>T0008@0.5</t>
         </is>
       </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>T0008@0.5</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -27335,6 +28375,11 @@
           <t>映像の母豚が妊娠前期かは不明（知識問題）。BCSで個体調整する前提</t>
         </is>
       </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>T0008@0.5</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -27486,6 +28531,11 @@
           <t>T0550@5</t>
         </is>
       </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>T0550@5</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -27642,6 +28692,11 @@
           <t>映像の乳房に明らかな異常は見えない（知識問題）</t>
         </is>
       </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>T0550@5</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -27793,6 +28848,11 @@
           <t>T0077@3</t>
         </is>
       </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>T0077@3</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -27949,6 +29009,11 @@
           <t>【社長確認】緑の数字が個体番号か(群番号・処置マーク等なら正解「1頭ずつ見分ける」が崩れる)。映像は後ろ姿で顔は写らない / 数字の意味（個体番号か群の番号か）を監修で確認</t>
         </is>
       </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>T0201@2</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -28105,6 +29170,11 @@
           <t>緊急かどうかの判断を問う問題なので難易度を中級→上級に修正(05_妊娠舎 報告フロー【緊急】横臥して起き上がれない と一致)</t>
         </is>
       </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>T0210@5</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -28261,6 +29331,11 @@
           <t>【社長確認】この映像が発情確認の背圧テストか(元命名は「陰部_触診」)。問い自体は「背中を押している」で映像どおりなのでそのまま。中級・上級の2問も同じ前提</t>
         </is>
       </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>T0618@0</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -28412,6 +29487,11 @@
           <t>T0618@0</t>
         </is>
       </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>T0618@0</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -28563,6 +29643,11 @@
           <t>T0618@0</t>
         </is>
       </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>T0618@0</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -28719,6 +29804,11 @@
           <t>en の he を中立表現に修正 / 背中に座る方法はmanualの背圧テスト（両手で押す）の変法。農場の実際のやり方か監修で確認</t>
         </is>
       </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>T0060@3</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -28870,6 +29960,11 @@
           <t>T0563@3</t>
         </is>
       </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>T0060@3</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -29026,6 +30121,11 @@
           <t>病名(子宮脱/膣脱/脱肛)は問わない。出血の映像あり</t>
         </is>
       </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>T0619@4</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -29177,6 +30277,11 @@
           <t>T0619@4</t>
         </is>
       </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>T0619@4</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -29333,6 +30438,11 @@
           <t>「何のため」=理由を問うので初級→中級</t>
         </is>
       </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>T0075@2</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -29484,6 +30594,11 @@
           <t>T0595@2</t>
         </is>
       </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>T0075@2</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -29640,6 +30755,11 @@
           <t>動画内にパドルボードは明確には写らない。知識問題として出題</t>
         </is>
       </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>T0143@3</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -29796,6 +30916,11 @@
           <t>精液保温器かどうかは映像から断定できない（上に『交配』ファイル）。監修で用途を確認。違えば削除</t>
         </is>
       </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>T0134@8</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -29952,6 +31077,11 @@
           <t>manual Q&amp;Aでは20〜22℃短時間は顕微鏡確認で使える場合ありと矛盾→25℃以上=使用中止の基準に合わせ26℃へ変更 / 同上：用途の確認が前提</t>
         </is>
       </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>T0134@8</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -30103,6 +31233,11 @@
           <t>T1041@0</t>
         </is>
       </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>T1041@0</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -30254,6 +31389,11 @@
           <t>T1081@0</t>
         </is>
       </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>T1081@0</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -30410,6 +31550,11 @@
           <t>根拠は06ではなく07_離乳舎の寝姿表にある→source修正(内容は一致) / 映像の子豚は散らばっていない（仮定の問い）</t>
         </is>
       </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>T1081@0</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -30561,6 +31706,11 @@
           <t>T1081@0</t>
         </is>
       </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>T1081@0</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -30717,6 +31867,11 @@
           <t>映像の子豚は重なっていない（仮定の問い）</t>
         </is>
       </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>T1085@0</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -30873,6 +32028,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>T0917@0</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -31029,6 +32189,11 @@
           <t>おがくずか戻し堆肥かは映像で断定できないため「おがくずなどの敷料」に｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>T0901@0</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -31185,6 +32350,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>T0903@0</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -31336,6 +32506,11 @@
           <t>T0903@0</t>
         </is>
       </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>T0903@0</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -31492,6 +32667,11 @@
           <t>manifestの命名は妊娠豚舎だが、写っているのは群飼の肥育豚/育成豚。舎名は問わない</t>
         </is>
       </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>T0970@0</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -31643,6 +32823,11 @@
           <t>T0970@0</t>
         </is>
       </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>T0970@0</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -31794,6 +32979,11 @@
           <t>T0973@1</t>
         </is>
       </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>T0973@1</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -31950,6 +33140,11 @@
           <t>右端に人の手・腕のみ</t>
         </is>
       </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>T0929@0</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -32101,6 +33296,11 @@
           <t>T1013@0</t>
         </is>
       </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>T1013@0</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -32252,6 +33452,11 @@
           <t>T1013@0</t>
         </is>
       </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>T1013@0</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -32408,6 +33613,11 @@
           <t>薬液注入器（ドサトロン型）と判断。監修で用途確認</t>
         </is>
       </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>T0921@0</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -32559,6 +33769,11 @@
           <t>T0921@0</t>
         </is>
       </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>T0921@0</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -32715,6 +33930,11 @@
           <t>空舎の洗浄と映像から断定はできない（豚は写らない）。洗浄→乾燥→消毒の順は知識問題</t>
         </is>
       </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>T0053@1</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -32871,6 +34091,11 @@
           <t>空舎の洗浄と映像から断定はできない（豚は写らない）。洗浄→乾燥→消毒の順は知識問題</t>
         </is>
       </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>T0053@1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -33027,6 +34252,11 @@
           <t>やや手ぶれ</t>
         </is>
       </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>T0931@0</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -33183,6 +34413,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>T0931@0</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -33339,6 +34574,11 @@
           <t>映像は窓ではなく換気扇の開口部の網→「換気口」に修正(manual: 換気口・開口部の防鳥ネット) / manifest命名=防鳥ネット</t>
         </is>
       </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>T0933@0</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -33495,6 +34735,11 @@
           <t>id の Rakun(アライグマ)→Anjing rakun(タヌキ)。イノシシは映像で明確(後半2〜6秒で接近) / 若いイノシシと判断（毛色・体形）。監修で確認</t>
         </is>
       </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>T0789@1</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -33651,6 +34896,11 @@
           <t>選択肢に病名（豚熱）が出るが、映像の豚の病名当てではなく侵入リスクの理由として記載</t>
         </is>
       </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>T0789@1</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -33802,6 +35052,11 @@
           <t>T0789@1</t>
         </is>
       </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>T0789@1</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -33953,6 +35208,11 @@
           <t>T0790@1</t>
         </is>
       </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>T0790@1</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -34104,6 +35364,11 @@
           <t>T0790@1</t>
         </is>
       </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>T0790@1</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -34255,6 +35520,11 @@
           <t>T0790@1</t>
         </is>
       </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>T0790@1</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -34406,6 +35676,11 @@
           <t>T0752@4</t>
         </is>
       </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>T0752@4</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -34562,6 +35837,11 @@
           <t>商品名が写る</t>
         </is>
       </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>T1015@0</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -34718,6 +35998,11 @@
           <t>T1015（アジタ容器）と連続の素材</t>
         </is>
       </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>T1021@0</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -34874,6 +36159,11 @@
           <t>虫の種類（ハエ/アブの幼虫）は問わない</t>
         </is>
       </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>T1030@0</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -35030,6 +36320,11 @@
           <t>出血の映像あり</t>
         </is>
       </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>T0623@0</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -35181,6 +36476,11 @@
           <t>T0623@0</t>
         </is>
       </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>T0623@0</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -35332,6 +36632,11 @@
           <t>T0630@1</t>
         </is>
       </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>T0080@1</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -35483,6 +36788,11 @@
           <t>T0630@1</t>
         </is>
       </c>
+      <c r="AL232" t="inlineStr">
+        <is>
+          <t>T0080@1</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -35639,6 +36949,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL233" t="inlineStr">
+        <is>
+          <t>W01@0</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -35790,6 +37105,11 @@
           <t>W01@154</t>
         </is>
       </c>
+      <c r="AL234" t="inlineStr">
+        <is>
+          <t>W01@154</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -35946,6 +37266,11 @@
           <t>注射の瞬間は274.5秒・276秒付近で首(耳のうしろ)に針先が見える(検証で実測)。</t>
         </is>
       </c>
+      <c r="AL235" t="inlineStr">
+        <is>
+          <t>W01@272.5</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -36097,6 +37422,11 @@
           <t>W01@272.5</t>
         </is>
       </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>W01@272.5</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -36248,6 +37578,11 @@
           <t>W01@200</t>
         </is>
       </c>
+      <c r="AL237" t="inlineStr">
+        <is>
+          <t>W01@200</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -36399,6 +37734,11 @@
           <t>W01@212</t>
         </is>
       </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>W01@212</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -36550,6 +37890,11 @@
           <t>W01@268</t>
         </is>
       </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>W01@268</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -36701,6 +38046,11 @@
           <t>W01@244</t>
         </is>
       </c>
+      <c r="AL240" t="inlineStr">
+        <is>
+          <t>W01@244</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -36857,6 +38207,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL241" t="inlineStr">
+        <is>
+          <t>W01@236</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -37013,6 +38368,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t>W01@252</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -37164,6 +38524,11 @@
           <t>W01@28</t>
         </is>
       </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t>W01@28</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -37320,6 +38685,11 @@
           <t>映像は注射の準備場面で、打っている薬の種類は映像からは分からない。問いは仮定の計算問題（manualの例題1と同じ数値）。</t>
         </is>
       </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t>W01@130</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -37476,6 +38846,11 @@
           <t>16.5秒付近で赤い帽子の人の横顔が写るため、start を 12.0→8.0 に変更(8〜13秒は通路と豚房のみ)。</t>
         </is>
       </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>W01@8</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -37632,6 +39007,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>W02@0</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -37788,6 +39168,11 @@
           <t>【社長確認】上部の黄色い筒状のものが巻き上げたカーテンであること(映像では筒=カーテンと断定しきれない)。 / 黄色い筒状のものが巻き上げたカーテンであることを監修で確認。</t>
         </is>
       </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>W15@18</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -37939,6 +39324,11 @@
           <t>W15@30</t>
         </is>
       </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>W15@30</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -38090,6 +39480,11 @@
           <t>W10@34</t>
         </is>
       </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>W10@34</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -38246,6 +39641,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>W14@8</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -38397,6 +39797,11 @@
           <t>W14@8</t>
         </is>
       </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t>W14@8</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -38548,6 +39953,11 @@
           <t>W03@8</t>
         </is>
       </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>W03@8</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -38699,6 +40109,11 @@
           <t>W06@3</t>
         </is>
       </c>
+      <c r="AL253" t="inlineStr">
+        <is>
+          <t>W06@3</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -38850,6 +40265,11 @@
           <t>W06@3</t>
         </is>
       </c>
+      <c r="AL254" t="inlineStr">
+        <is>
+          <t>W06@3</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -39006,6 +40426,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / カードの文字は読めない解像度。個人情報なし。</t>
         </is>
       </c>
+      <c r="AL255" t="inlineStr">
+        <is>
+          <t>W07@2</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -39157,6 +40582,11 @@
           <t>W07@14</t>
         </is>
       </c>
+      <c r="AL256" t="inlineStr">
+        <is>
+          <t>W07@14</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -39313,6 +40743,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 映像の薬がワクチンかは映像だけでは断定できないため、問いは「母豚に打つワクチンは」と一般化している。</t>
         </is>
       </c>
+      <c r="AL257" t="inlineStr">
+        <is>
+          <t>W04@30</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -39469,6 +40904,11 @@
           <t>22〜24秒がカメラ移動でブレるため start を 20.0→17.0 に変更(17〜22秒=薬びん・注射器・母豚が安定して写る。既存q08と同じ窓だが問いは別観点)。</t>
         </is>
       </c>
+      <c r="AL258" t="inlineStr">
+        <is>
+          <t>W04@17</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -39625,6 +41065,11 @@
           <t>22〜24秒がカメラ移動でブレるため start を 20.0→17.0 に変更(q28と同じ窓)。｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL259" t="inlineStr">
+        <is>
+          <t>W04@17</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -39776,6 +41221,11 @@
           <t>W09@42</t>
         </is>
       </c>
+      <c r="AL260" t="inlineStr">
+        <is>
+          <t>W09@42</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -39932,6 +41382,11 @@
           <t>子豚の日齢は映像から推定（分娩柵内）。</t>
         </is>
       </c>
+      <c r="AL261" t="inlineStr">
+        <is>
+          <t>W12@26.5</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -40088,6 +41543,11 @@
           <t>【社長確認】31.5秒の箱(ふたに丸い穴)が保温箱で、33〜36秒に子豚が集まっている囲いがその箱の中であること。 / ふたの丸い穴が保温灯用で、箱が保温箱であることを監修で確認。</t>
         </is>
       </c>
+      <c r="AL262" t="inlineStr">
+        <is>
+          <t>W13@31.5</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -40244,6 +41704,11 @@
           <t>奥に防護服の人が小さく写る（顔は判別できない）。はかりであることを監修で確認。</t>
         </is>
       </c>
+      <c r="AL263" t="inlineStr">
+        <is>
+          <t>W19@11</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -40395,6 +41860,11 @@
           <t>W19@11</t>
         </is>
       </c>
+      <c r="AL264" t="inlineStr">
+        <is>
+          <t>W19@11</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -40546,6 +42016,11 @@
           <t>W19@38</t>
         </is>
       </c>
+      <c r="AL265" t="inlineStr">
+        <is>
+          <t>W19@38</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -40697,6 +42172,11 @@
           <t>W19@38</t>
         </is>
       </c>
+      <c r="AL266" t="inlineStr">
+        <is>
+          <t>W19@38</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -40853,6 +42333,11 @@
           <t>【社長確認】入口横の青いトレー(液入り・白いボトルが隣)が踏み込み消毒槽であること。46秒以降の横顔は5秒窓の外で回避済み。 / 青い容器が踏み込み消毒槽であることを監修で要確認。46秒付近から人の横顔が写るため、start=40.8で45.8秒までに収めた。</t>
         </is>
       </c>
+      <c r="AL267" t="inlineStr">
+        <is>
+          <t>W20@40.8</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -41009,6 +42494,11 @@
           <t>40と同じ素材。容器が消毒槽であることの確認が前提。</t>
         </is>
       </c>
+      <c r="AL268" t="inlineStr">
+        <is>
+          <t>W20@40.8</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -41165,6 +42655,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL269" t="inlineStr">
+        <is>
+          <t>W20@126</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -41321,6 +42816,11 @@
           <t>【社長確認】豚房内の四角い金属の箱が給餌器であること(水槽の可能性を否定できない)。 / 四角い金属の箱が給餌器であることを監修で確認。</t>
         </is>
       </c>
+      <c r="AL270" t="inlineStr">
+        <is>
+          <t>W20@126</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -41477,6 +42977,11 @@
           <t>映像は見回りの場面。群れから離れた豚が写っているとは限らないため、問いは仮定の形。</t>
         </is>
       </c>
+      <c r="AL271" t="inlineStr">
+        <is>
+          <t>W20@174</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -41633,6 +43138,11 @@
           <t>解剖の場面（刃物・出血少量）。既存q14と同じ動画だが別の時刻・別の観点。病名は問わない。</t>
         </is>
       </c>
+      <c r="AL272" t="inlineStr">
+        <is>
+          <t>W21@24</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -41784,6 +43294,11 @@
           <t>W21@24</t>
         </is>
       </c>
+      <c r="AL273" t="inlineStr">
+        <is>
+          <t>W21@24</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -41935,6 +43450,11 @@
           <t>W21@24</t>
         </is>
       </c>
+      <c r="AL274" t="inlineStr">
+        <is>
+          <t>W21@24</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -42086,6 +43606,11 @@
           <t>W21@250</t>
         </is>
       </c>
+      <c r="AL275" t="inlineStr">
+        <is>
+          <t>W21@250</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -42242,6 +43767,11 @@
           <t>胃の内容物（飼料）と判断。監修で確認を。</t>
         </is>
       </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>W21@320</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -42393,6 +43923,11 @@
           <t>W21@252</t>
         </is>
       </c>
+      <c r="AL277" t="inlineStr">
+        <is>
+          <t>W21@252</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -42549,6 +44084,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL278" t="inlineStr">
+        <is>
+          <t>W21@380</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -42700,6 +44240,11 @@
           <t>W21@438</t>
         </is>
       </c>
+      <c r="AL279" t="inlineStr">
+        <is>
+          <t>W21@438</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -42856,6 +44401,11 @@
           <t>【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した</t>
         </is>
       </c>
+      <c r="AL280" t="inlineStr">
+        <is>
+          <t>W21@388</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -43007,6 +44557,11 @@
           <t>W21@448</t>
         </is>
       </c>
+      <c r="AL281" t="inlineStr">
+        <is>
+          <t>W21@448</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -43163,6 +44718,11 @@
           <t>【社長確認】給水カップ周りの濡れが水もれ/流量過多で、飲水時のふつうの濡れではないこと(映像だけでは断定不可)。窓の終わりに遠くの人が小さく映るが顔は判別不能。｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 一時的なこぼれの可能性もある。窓の終わり近くに遠くの人が小さく映る（顔は判別できない程度）。監修で確認を。</t>
         </is>
       </c>
+      <c r="AL282" t="inlineStr">
+        <is>
+          <t>W22@138.5</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -43314,6 +44874,11 @@
           <t>W22@84</t>
         </is>
       </c>
+      <c r="AL283" t="inlineStr">
+        <is>
+          <t>W22@84</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -43470,6 +45035,11 @@
           <t>既存q30（血を何に使うか）と近い。道具（採血管）の識別として別観点。</t>
         </is>
       </c>
+      <c r="AL284" t="inlineStr">
+        <is>
+          <t>W24@10</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -43621,6 +45191,11 @@
           <t>W24@57</t>
         </is>
       </c>
+      <c r="AL285" t="inlineStr">
+        <is>
+          <t>W24@57</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -43772,6 +45347,11 @@
           <t>W24@60.5</t>
         </is>
       </c>
+      <c r="AL286" t="inlineStr">
+        <is>
+          <t>W24@60.5</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -43923,6 +45503,11 @@
           <t>W24@62</t>
         </is>
       </c>
+      <c r="AL287" t="inlineStr">
+        <is>
+          <t>W24@62</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -44079,6 +45664,11 @@
           <t>知識問題。映像の柵に掛けた白いビニール袋の用途は不明（針を入れている場面ではない）。</t>
         </is>
       </c>
+      <c r="AL288" t="inlineStr">
+        <is>
+          <t>W24@108</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -44230,6 +45820,11 @@
           <t>W24@120</t>
         </is>
       </c>
+      <c r="AL289" t="inlineStr">
+        <is>
+          <t>W24@120</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -44386,6 +45981,11 @@
           <t>manualはロープ（スノートロープ）の記述。映像は棒つきのワイヤー保定器だが、かける位置は同じ。既存q12/q28は目的・対象豚を問うもので観点が違う。</t>
         </is>
       </c>
+      <c r="AL290" t="inlineStr">
+        <is>
+          <t>W24@196</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -44537,6 +46137,11 @@
           <t>W24@235</t>
         </is>
       </c>
+      <c r="AL291" t="inlineStr">
+        <is>
+          <t>W24@235</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -44688,6 +46293,11 @@
           <t>W24@237</t>
         </is>
       </c>
+      <c r="AL292" t="inlineStr">
+        <is>
+          <t>W24@237</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -44839,6 +46449,11 @@
           <t>W24@116</t>
         </is>
       </c>
+      <c r="AL293" t="inlineStr">
+        <is>
+          <t>W24@116</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -44990,6 +46605,11 @@
           <t>W23@2</t>
         </is>
       </c>
+      <c r="AL294" t="inlineStr">
+        <is>
+          <t>W23@2</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -45141,6 +46761,11 @@
           <t>W23@2</t>
         </is>
       </c>
+      <c r="AL295" t="inlineStr">
+        <is>
+          <t>W23@2</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -45297,6 +46922,11 @@
           <t>28〜30.5秒はカメラが大きく振れて全面ブレ(手・黒い物体が入る)。安定して豚が向かってくる30.5秒に移動</t>
         </is>
       </c>
+      <c r="AL296" t="inlineStr">
+        <is>
+          <t>W23@30.5</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -45453,6 +47083,11 @@
           <t>28〜30.5秒がブレのため30.5秒に移動</t>
         </is>
       </c>
+      <c r="AL297" t="inlineStr">
+        <is>
+          <t>W23@30.5</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -45609,6 +47244,11 @@
           <t>28〜30.5秒がブレのため30.5秒に移動</t>
         </is>
       </c>
+      <c r="AL298" t="inlineStr">
+        <is>
+          <t>W23@30.5</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -45760,6 +47400,11 @@
           <t>W23@30.5</t>
         </is>
       </c>
+      <c r="AL299" t="inlineStr">
+        <is>
+          <t>W23@30.5</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -45911,6 +47556,11 @@
           <t>W23@30.5</t>
         </is>
       </c>
+      <c r="AL300" t="inlineStr">
+        <is>
+          <t>W23@30.5</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -46067,6 +47717,11 @@
           <t>36秒開始だと39〜41秒でカメラが振れて天井だけになる。34秒開始(34〜39秒)なら青い印の豚が遠景→近景で写る(37秒に軽いブレあり) / 映像の青い印の意味（なぜ付けたか）は問うていない。一般論として出題</t>
         </is>
       </c>
+      <c r="AL301" t="inlineStr">
+        <is>
+          <t>W23@34</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -46223,6 +47878,11 @@
           <t>36秒開始だと後半が天井だけになるため34秒開始に移動</t>
         </is>
       </c>
+      <c r="AL302" t="inlineStr">
+        <is>
+          <t>W23@34</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -46379,6 +48039,11 @@
           <t>カテゴリが衛生・防疫だったが内容は肥育豚の観察なので肉豚・出荷・肉へ。映像は103〜105秒で豚が見え、以降は作業者の足と袋で一部隠れるが「コンクリート床に1頭」は判別できる</t>
         </is>
       </c>
+      <c r="AL303" t="inlineStr">
+        <is>
+          <t>W23@103</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -46535,6 +48200,11 @@
           <t>豚は既に豚房外(コンクリート床)に出されており、生死は映像から判別できない。問いは見えるようす(横倒し・動かない)だけを聞く。286〜288秒に麦わら帽子・赤手袋の作業者が真上から写るが顔は帽子で隠れる(1秒刻みで確認済み)</t>
         </is>
       </c>
+      <c r="AL304" t="inlineStr">
+        <is>
+          <t>W23@284</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -46689,6 +48359,11 @@
       <c r="AK305" t="inlineStr">
         <is>
           <t>映像の豚が「立てない」とは言い切れないため、問いの前提を映像の断定から一般の場面に変更(4言語) / 映像は横倒しの豚(生死不明)。問いは映像の豚を「立てない」と断定しない形にした</t>
+        </is>
+      </c>
+      <c r="AL305" t="inlineStr">
+        <is>
+          <t>W23@284</t>
         </is>
       </c>
     </row>

--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -6165,12 +6165,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>帳面の「種雄番号」の欄に、数字が2つや3つ書いてあります。何を表していますか？</t>
+          <t>帳面の「種雄番号」の欄には、何を書きますか？</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2〜3回の種付けで使った雄（精液）の番号</t>
+          <t>種付けに使った雄（精液）の番号</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6193,52 +6193,52 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>種付けは1回の発情で2〜3回行い、そのたびに使った雄（精液）の番号を書きます。</t>
+          <t>種付けのたびに、使った雄（精液）の番号を「種雄番号」の欄に書きます。あとで受胎や成績をふり返るときに使います。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>In the "boar number" column, there are two or three numbers in a row. What do they mean?</t>
+          <t>What do you write in the "boar number" column of the record book?</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>The boar (semen) number used for each of 2–3 breedings</t>
+          <t>The number of the boar (semen) used for mating</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>The number of piglets born and the number that died</t>
+          <t>The number of piglets born and died</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Which birth this is for the sow</t>
+          <t>How many litters the sow has had</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>The daily feed amount in kg</t>
+          <t>The daily feed amount (kg)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Trong cột "số heo đực" có 2 hoặc 3 con số trên một dòng. Chúng có nghĩa gì?</t>
+          <t>Cột "số heo đực" trong sổ ghi chép dùng để ghi gì?</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Số heo đực (tinh) đã dùng cho 2–3 lần phối</t>
+          <t>Số của heo đực (tinh) đã dùng để phối</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Số heo con sinh ra và số con chết</t>
+          <t>Số heo con sinh ra và số heo con chết</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Heo nái đẻ lứa thứ mấy</t>
+          <t>Heo nái này đẻ lứa thứ mấy</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Di kolom "nomor pejantan" ada 2 atau 3 angka dalam satu baris. Apa artinya?</t>
+          <t>Apa yang ditulis di kolom "nomor pejantan" pada buku catatan?</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Nomor pejantan (semen) untuk 2–3 kali kawin</t>
+          <t>Nomor pejantan (semen) yang dipakai untuk kawin</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Jumlah anak babi lahir dan yang mati</t>
+          <t>Jumlah anak babi yang lahir dan yang mati</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Paritas induk (beranak ke berapa)</t>
+          <t>Induk ini beranak untuk yang ke berapa</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>【社長確認】種雄番号欄の3つの数字＝3回の授精ごとの雄番号という解釈は帳面から推定したもの（manualは2回交配推奨・3回は状況次第）。行によっては4つ目の小さい数字もある。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】1行に番号が2〜3個（4個目もある）＝授精回数という解釈は睦沢の記入ルール依存。回数を問わず「種雄番号欄に書くもの」だけを問う形に変更。 / (元)種雄番号欄の3つの数字＝3回の授精ごとの雄番号という解釈は帳面から推定したもの（manualは2回交配推奨・3回は状況次第）。行によっては4つ目の小さい数字もある。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -6326,27 +6326,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>帳面の交配月日に「pm」と書き足した日付があります。何を表していますか？</t>
+          <t>種付けの記録には、日付だけでなく午前・午後（時刻）も書きます。なぜですか？</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>午後に種付けした</t>
+          <t>次の種付けをする時間を決めるため（時間の間かくが大切）</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>薬を打った</t>
+          <t>えさをやる時間を決めるため</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>母豚が死んだ</t>
+          <t>母豚の体重を計算するため</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>分娩した</t>
+          <t>出荷する日を決めるため</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -6354,82 +6354,82 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>種付けは時間が大切なので、日付だけでなく午前か午後かも記録します。「pm」は午後に種付けしたという意味です。</t>
+          <t>種付けは1回目から12〜16時間ほどあけて次を行います。時間の間かくが大切なので、日付だけでなく午前か午後かも記録します。</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Some breeding dates have "pm" written after them. What does "pm" mean?</t>
+          <t>In mating records, you write not only the date but also AM/PM (the time). Why?</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>The sow was bred in the afternoon</t>
+          <t>To decide the time of the next insemination (the interval matters)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Medicine was given</t>
+          <t>To decide the feeding time</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>The sow died</t>
+          <t>To calculate the sow's weight</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>The sow farrowed</t>
+          <t>To decide the shipping date</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Có ngày phối được ghi thêm chữ "pm". "pm" nghĩa là gì?</t>
+          <t>Khi ghi sổ phối giống, ngoài ngày còn ghi sáng/chiều (giờ). Vì sao?</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Phối vào buổi chiều</t>
+          <t>Để quyết định giờ phối lần tiếp theo (khoảng cách thời gian rất quan trọng)</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Đã tiêm thuốc</t>
+          <t>Để quyết định giờ cho ăn</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Heo nái đã chết</t>
+          <t>Để tính cân nặng heo nái</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Heo nái đã đẻ</t>
+          <t>Để quyết định ngày xuất chuồng</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Ada tanggal kawin yang diberi tulisan "pm". Apa arti "pm"?</t>
+          <t>Pada catatan kawin, selain tanggal juga ditulis pagi/sore (jam). Mengapa?</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Dikawinkan pada sore hari</t>
+          <t>Untuk menentukan jam kawin berikutnya (jarak waktunya penting)</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Sudah diberi obat</t>
+          <t>Untuk menentukan jam pemberian pakan</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Induk sudah mati</t>
+          <t>Untuk menghitung berat induk</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Induk sudah beranak</t>
+          <t>Untuk menentukan tanggal jual</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>【社長確認】「pm」＝午後の種付けは一般的な略記からの推定でmanualに明記なし（manualは授精日時の記録を求めるのみ）。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】「pm」の略記の意味は帳面の書き方（現場ルール）に依存し manual に明記なし。略記を問わず「時刻まで記録する理由」を問う形に変更（manual 04: 授精日時の記録・2回目は12〜16時間後）。 / (元)「pm」＝午後の種付けは一般的な略記からの推定でmanualに明記なし（manualは授精日時の記録を求めるのみ）。睦沢の記入ルールを確認。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -8419,27 +8419,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>種付け（人工授精）の回数と間隔で、マニュアルで標準とされているのはどれですか？</t>
+          <t>人工授精を1回目にしたあと、2回目はどのくらいあけて行いますか？</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2回。2回目は1回目の12〜16時間後</t>
+          <t>12〜16時間後（半日ほどあと）</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1回だけ。2回目はしない</t>
+          <t>1時間後（すぐに）</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2回。2回目は1回目の1週間後</t>
+          <t>1週間後</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5回。毎日1回ずつ5日間</t>
+          <t>1か月後</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -8447,87 +8447,87 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>マニュアルでは2回交配が標準で、2回目は1回目から12〜16時間後に行います。</t>
+          <t>2回目の授精は1回目から12〜16時間後が目安です。回数（2回か3回か）は農場のルールに従います。</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>According to the manual, what is the standard number and timing of inseminations?</t>
+          <t>After the first artificial insemination, how long do you wait before the second one?</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Twice; the 2nd is 12–16 hours after the 1st</t>
+          <t>12 to 16 hours later (about half a day)</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Only once; no 2nd time</t>
+          <t>1 hour later (right away)</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Twice; the 2nd is one week after the 1st</t>
+          <t>1 week later</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Five times; once a day for 5 days</t>
+          <t>1 month later</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Theo sổ tay, số lần phối (thụ tinh nhân tạo) và khoảng cách tiêu chuẩn là gì?</t>
+          <t>Sau khi thụ tinh nhân tạo lần 1, cách bao lâu thì làm lần 2?</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2 lần; lần 2 cách lần 1 từ 12–16 giờ</t>
+          <t>Sau 12–16 giờ (khoảng nửa ngày)</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Chỉ 1 lần; không phối lần 2</t>
+          <t>Sau 1 giờ (ngay lập tức)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2 lần; lần 2 cách lần 1 một tuần</t>
+          <t>Sau 1 tuần</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>5 lần; mỗi ngày 1 lần trong 5 ngày</t>
+          <t>Sau 1 tháng</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Menurut manual, berapa kali dan jarak kawin suntik (IB) yang standar?</t>
+          <t>Setelah inseminasi buatan pertama, berapa lama menunggu sebelum yang kedua?</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2 kali; yang ke-2 12–16 jam setelah yang pertama</t>
+          <t>12–16 jam kemudian (kira-kira setengah hari)</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Hanya 1 kali; tidak ada yang ke-2</t>
+          <t>1 jam kemudian (langsung)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2 kali; yang ke-2 seminggu setelah yang pertama</t>
+          <t>1 minggu kemudian</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>5 kali; sehari sekali selama 5 hari</t>
+          <t>1 bulan kemudian</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>上級</t>
+          <t>中級</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>【社長確認】manualは2回交配推奨だが、帳面は1行に雄番号が3つ（3回授精）の行が大半＝睦沢は3回の可能性。現場ルールと矛盾するなら出題しない方がよい。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】manual は「2回交配が標準だが農場の方針による」と明記し、帳面は3回の可能性が高い。回数を問わず、2回・3回どちらのパターンでも共通の「次の種付けまでの間かく（約12時間）」を問う形に変更。 / (元)manualは2回交配推奨だが、帳面は1行に雄番号が3つ（3回授精）の行が大半＝睦沢は3回の可能性。現場ルールと矛盾するなら出題しない方がよい。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認）｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>分娩予定日が1月1日の母豚です。「分娩予定の2〜4週間前」に打つワクチンは、いつごろ打ちますか？</t>
+          <t>あるワクチンは「分娩予定の2〜4週間前に打つ」と決められているとします。分娩予定日が1月1日の母豚なら、いつごろ打ちますか？</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8769,42 +8769,42 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>分娩予定日からさかのぼってワクチンの日を決めます。例として大腸菌ワクチンは分娩予定の2〜4週間前です（実際は農場の獣医師が決めたプログラムに従う）。</t>
+          <t>1月1日から2週間前は12月18日、4週間前は12月4日です。実際にいつ何を打つかは、農場の獣医師が決めたプログラムに従います。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>A sow's expected farrowing date is January 1. When should a vaccine given "2-4 weeks before farrowing" be given?</t>
+          <t>Suppose a vaccine must be given "2 to 4 weeks before the expected farrowing date". If a sow is due on January 1, about when do you give it?</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Around December 4-18</t>
+          <t>Around December 4 to 18</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>On January 1</t>
+          <t>On January 1 itself</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Around January 15-29</t>
+          <t>Around January 15 to 29</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Around September (when she was bred)</t>
+          <t>Around September (at mating)</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Heo nái có ngày dự kiến đẻ là 1/1. Vắc-xin tiêm "2-4 tuần trước khi đẻ" thì tiêm khoảng khi nào?</t>
+          <t>Giả sử một loại vắc-xin được quy định "tiêm trước ngày đẻ dự kiến 2–4 tuần". Heo nái dự kiến đẻ ngày 1/1 thì tiêm vào khoảng nào?</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Khoảng ngày 4-18/12</t>
+          <t>Khoảng ngày 4–18 tháng 12</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -8814,37 +8814,37 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Khoảng ngày 15-29/1</t>
+          <t>Khoảng ngày 15–29 tháng 1</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Khoảng tháng 9 (lúc phối)</t>
+          <t>Khoảng tháng 9 (lúc phối giống)</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Perkiraan beranak induk ini tanggal 1 Januari. Vaksin yang diberikan "2-4 minggu sebelum beranak" diberikan kapan?</t>
+          <t>Misalkan sebuah vaksin ditentukan "diberikan 2–4 minggu sebelum tanggal perkiraan beranak". Jika induk diperkirakan beranak 1 Januari, kira-kira kapan divaksin?</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Sekitar 4-18 Desember</t>
+          <t>Sekitar 4–18 Desember</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Tepat 1 Januari</t>
+          <t>Tepat tanggal 1 Januari</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Sekitar 15-29 Januari</t>
+          <t>Sekitar 15–29 Januari</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Sekitar September (saat dikawinkan)</t>
+          <t>Sekitar September (saat kawin)</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>【社長確認】manualの大腸菌ワクチン例（分娩予定2〜4週前）に沿った計算問だが、睦沢の注射カレンダーは交配日基準。現場の実プログラムと食い違うなら差し替え。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】睦沢の注射カレンダーは交配日基準で、分娩予定基準の大腸菌ワクチンは現場と食い違う恐れ。「そのワクチンが分娩予定2〜4週前と決められているとしたら」の仮定形にして日付計算だけを問う。 / (元)manualの大腸菌ワクチン例（分娩予定2〜4週前）に沿った計算問だが、睦沢の注射カレンダーは交配日基準。現場の実プログラムと食い違うなら差し替え。rotate 90→0（原画像はEXIF回転で既に正立。cut_clips_v2はexif_transpose後にさらに回すため90°だと横倒しになるのを実クリップで確認） / 960x540では帳面の題名は読めるが列見出し・手書きは判読不可。答えは問題文だけで決まる。 元画像は回転不要（rotate=0）。</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>肉豚・出荷・肉</t>
+          <t>衛生・防疫</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -12872,27 +12872,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>豚の体に、かまれたような傷がたくさんあります。多い原因はどれですか？</t>
+          <t>豚の体に傷やかさぶたがたくさんあるのを見つけました。どうしますか？</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ほかの豚とのけんか（せまい・過密など）</t>
+          <t>上司に知らせて、けんかや過密（せまさ）がないか群れの様子も確かめる</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>えさの食べすぎ（太りすぎなど）</t>
+          <t>そのままにして、しばらく様子を見る</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>水の飲みすぎ（おなかの冷えなど）</t>
+          <t>水をかけて洗い流せばよい</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>日光の当たりすぎ（日焼けなど）</t>
+          <t>えさの量を減らす</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -12900,82 +12900,82 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>体の傷が多いのは、けんか（闘争）のサインのことが多く、過密などのストレスが原因になります。</t>
+          <t>体の傷が多いのは、けんか（闘争）や過密のサインのことが多い異常です。すぐに上司に報告し、群れの様子も確かめます。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>A pig has many bite-like wounds on its body. What is a common cause?</t>
+          <t>You find a pig with many wounds and scabs on its body. What do you do?</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Fighting with other pigs (crowding, too little space)</t>
+          <t>Tell your supervisor and also check the group for fighting or overcrowding</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Eating too much feed (getting too fat)</t>
+          <t>Leave it and just watch for a while</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Drinking too much water (cold stomach)</t>
+          <t>Just rinse it off with water</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Too much sunlight (sunburn)</t>
+          <t>Reduce the amount of feed</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Trên mình heo có nhiều vết thương như bị cắn. Nguyên nhân thường gặp là gì?</t>
+          <t>Bạn thấy một con heo có nhiều vết thương và vảy trên mình. Bạn làm gì?</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Cắn nhau với heo khác (chuồng chật, nuôi quá dày)</t>
+          <t>Báo cấp trên và kiểm tra cả đàn xem có đánh nhau hay quá chật không</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Ăn quá nhiều (bị béo phì)</t>
+          <t>Để vậy, theo dõi thêm một thời gian</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Uống quá nhiều nước (lạnh bụng)</t>
+          <t>Chỉ cần xịt nước rửa sạch</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Phơi nắng quá nhiều (cháy nắng)</t>
+          <t>Giảm lượng cám</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>Babi ini banyak luka seperti bekas gigitan. Apa penyebab yang sering terjadi?</t>
+          <t>Anda menemukan babi dengan banyak luka dan koreng di badannya. Apa yang Anda lakukan?</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Berkelahi dengan babi lain (sempit, terlalu padat)</t>
+          <t>Lapor ke atasan dan periksa juga kelompoknya, apakah ada perkelahian atau terlalu padat</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>Makan terlalu banyak (kegemukan)</t>
+          <t>Dibiarkan dulu, diamati beberapa waktu</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>Minum terlalu banyak (perut dingin)</t>
+          <t>Cukup disiram air sampai bersih</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Terlalu banyak kena matahari (terbakar matahari)</t>
+          <t>Mengurangi jumlah pakan</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>【社長確認】傷がけんか由来かは写真で断定できない(こすれ・皮膚病の可能性)。manual 08は「皮膚の傷が多い=闘争や圧迫」｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 傷の原因は写真だけでは断定できないため「多い原因」として問うた / 【QA】同じ場面の q93 の答え（傷がたくさん）を問題文に含む。どちらか一方にするか検討</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】傷がかみ傷か写真で断定できず、また q93（同じ豚の写真）の答えを問題文に含んでいた。原因を断定せず「傷を見つけたらどうするか」（manual 08/20: 報告・過密やけんかの確認）に変更。カテゴリは母豚のため「衛生・防疫」が適切。 / (元)傷がけんか由来かは写真で断定できない(こすれ・皮膚病の可能性)。manual 08は「皮膚の傷が多い=闘争や圧迫」｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 傷の原因は写真だけでは断定できないため「多い原因」として問うた / 【QA】同じ場面の q93 の答え（傷がたくさん）を問題文に含む。どちらか一方にするか検討</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>母豚のカードの「死亡」のらんには、何を書きますか？</t>
+          <t>分娩のあと、子豚が死にました。記録（カードや帳面）に何を書きますか？</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>子豚が死んだ日と頭数</t>
+          <t>死んだ日と頭数</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13061,17 +13061,17 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>カードの「死亡」らんには、子豚が死んだ日と頭数を書きます。写真のカードでは11頭から7頭に減っています。</t>
+          <t>子豚が死んだら、死んだ日と頭数を記録します。写真のカードでも、日付ごとに減った頭数が書かれています。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>What is written in the "deaths" column of the sow card?</t>
+          <t>After farrowing, a piglet died. What do you write in the record (card or book)?</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>The date and number of piglets that died</t>
+          <t>The date and the number of piglets that died</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -13086,17 +13086,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>The name of the medicine</t>
+          <t>The name of a medicine</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Trong cột "chết" trên thẻ heo nái, ghi gì?</t>
+          <t>Sau khi đẻ, có heo con chết. Bạn ghi gì vào sổ (thẻ hoặc sổ ghi chép)?</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Ngày và số heo con bị chết</t>
+          <t>Ngày chết và số con chết</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Lượng thức ăn</t>
+          <t>Lượng cám</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>Apa yang ditulis di kolom "mati" pada kartu induk?</t>
+          <t>Setelah beranak, ada anak babi yang mati. Apa yang ditulis di catatan (kartu atau buku)?</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>【社長確認】カードの文字はスマホ画面では読めない(縦写真・小文字)ため問いは知識問題として成立させ、難易度を初級へ。カード様式は農場ごと(写真は高橋さん農場)なのでヒラノの様式と合うか確認 / カードの文字はスマホでは読めない前提(問いは文字を読まずに答えられる)。カード様式は農場ごとに異なる</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】カード様式（「死亡」らん）は農場ごとに違い、写真は高橋さん農場のもの。カードの様式に依存せず「子豚が死んだとき記録に何を書くか」（03_共通業務 死亡状況の記録）を問う。 / (元)カードの文字はスマホ画面では読めない(縦写真・小文字)ため問いは知識問題として成立させ、難易度を初級へ。カード様式は農場ごと(写真は高橋さん農場)なのでヒラノの様式と合うか確認 / カードの文字はスマホでは読めない前提(問いは文字を読まずに答えられる)。カード様式は農場ごとに異なる</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
@@ -13989,27 +13989,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>動画の床にある黄色いものは何ですか？</t>
+          <t>動画の床に黄色いものがあります。子豚の糞（ふん）の色で、ふつう（正常）なのはどれですか？</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>子豚のやわらかい糞（下痢）</t>
+          <t>茶色〜こげ茶色</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>子豚にあげたえさの粉</t>
+          <t>黄色</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>床にまいた消毒の粉</t>
+          <t>緑色</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>床にこぼれた母豚の乳</t>
+          <t>黒色（血がまじる）</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -14017,82 +14017,82 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>床の黄色くやわらかいものは子豚の下痢の糞です。黄色い糞は異常のサインです。</t>
+          <t>ふつうの糞は茶色〜こげ茶色です。黄色・緑色・黒色の糞や、水のような糞は異常のサインなので報告します。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>What is the yellow thing on the floor in the video?</t>
+          <t>There is something yellow on the floor in the video. Which color of piglet feces is normal?</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Soft piglet feces (diarrhea)</t>
+          <t>Brown to dark brown</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Feed powder given to the piglets</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Disinfectant powder spread on the floor</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Sow's milk spilled on the floor</t>
+          <t>Black (with blood)</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Thứ màu vàng trên sàn trong video là gì?</t>
+          <t>Trên sàn trong video có thứ màu vàng. Phân heo con màu nào là bình thường?</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Phân lỏng của heo con (tiêu chảy)</t>
+          <t>Màu nâu đến nâu sẫm</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Bột cám cho heo con ăn</t>
+          <t>Màu vàng</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Bột sát trùng rắc trên sàn</t>
+          <t>Màu xanh lá</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Sữa nái đổ trên sàn</t>
+          <t>Màu đen (có lẫn máu)</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>Benda kuning di lantai dalam video itu apa?</t>
+          <t>Di lantai pada video ada sesuatu berwarna kuning. Warna kotoran anak babi yang normal adalah?</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Kotoran lembek anak babi (diare)</t>
+          <t>Cokelat sampai cokelat tua</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>Bubuk pakan untuk anak babi</t>
+          <t>Kuning</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>Bubuk disinfektan yang ditabur di lantai</t>
+          <t>Hijau</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Susu induk yang tumpah di lantai</t>
+          <t>Hitam (bercampur darah)</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>【社長確認】床の黄色いものが子豚の下痢便で間違いないか（嘔吐物の可能性）。見て判断が要るため難易度を中級に変更｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 床の黄色いペースト状のものが下痢便か嘔吐物か写真だけでは断定できない</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】床の黄色いものが下痢便か嘔吐物かは映像で断定不可。「黄色いもの」を断定せず、manual 20 の糞の色（正常＝茶〜暗褐色、黄色・緑・黒は異常）を問う形に変更。q89 とは観点が違う。 / (元)床の黄色いものが子豚の下痢便で間違いないか（嘔吐物の可能性）。見て判断が要るため難易度を中級に変更｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 床の黄色いペースト状のものが下痢便か嘔吐物か写真だけでは断定できない</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>【社長確認】写真の豚は母豚(台帳『母豚_横臥』)で肥育カテゴリは不適。背中の病変がかみ傷と断定できないため正解を『傷やかさぶたがたくさんある』に変更・カテゴリを衛生・防疫へ / 写真の豚は母豚と思われ（台帳『母豚_横臥』）、傷がかみ傷かは断定できない / 【QA】同じ場面の q81 の問題文（かまれたような傷）がこの問いの答えを含む（同じ回に出る確率は約1%）</t>
+          <t>【解決済 09-24 Fable判断: そのまま採用】映像どおり「傷やかさぶたがたくさんある」を問うだけで原因は断定しておらず、カテゴリも衛生・防疫に直し済み。q81 の作り替えで答えの重複も解消。 / (元)写真の豚は母豚(台帳『母豚_横臥』)で肥育カテゴリは不適。背中の病変がかみ傷と断定できないため正解を『傷やかさぶたがたくさんある』に変更・カテゴリを衛生・防疫へ / 写真の豚は母豚と思われ（台帳『母豚_横臥』）、傷がかみ傷かは断定できない / 【QA】同じ場面の q81 の問題文（かまれたような傷）がこの問いの答えを含む（同じ回に出る確率は約1%）</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
@@ -17627,27 +17627,27 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>豚舎の間の通路に、白い粉がまかれています。この白い粉は何のためですか？</t>
+          <t>豚舎と豚舎の間の通路に、消石灰（白い粉）をまいてあります。何のためですか？</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>消石灰で、地面を消毒するため</t>
+          <t>地面のウイルスや菌を消毒するため</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>雪が積もったため</t>
+          <t>すべり止めのため</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>豚のえさがこぼれたため</t>
+          <t>豚のえさにするため</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>すべり止めの砂</t>
+          <t>地面を白くしてきれいに見せるため</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -17655,82 +17655,82 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>通路の白い粉は消石灰です。強いアルカリで、地面のウイルスや菌を消毒します。</t>
+          <t>消石灰は強いアルカリで、地面のウイルスや菌を消毒します。農場の出入口や通路によく使います。</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>White powder has been spread on the path between barns. What is it for?</t>
+          <t>Slaked lime (white powder) has been spread on the path between pig houses. What is it for?</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>It is slaked lime, used to disinfect the ground</t>
+          <t>To disinfect viruses and germs on the ground</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Snow has piled up</t>
+          <t>To stop people from slipping</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Pig feed was spilled</t>
+          <t>To use as pig feed</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Sand to prevent slipping</t>
+          <t>To make the ground look white and clean</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Bột trắng được rải trên lối đi giữa các chuồng. Bột này để làm gì?</t>
+          <t>Trên lối đi giữa các chuồng có rải vôi tôi (bột trắng). Để làm gì?</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Là vôi bột, dùng để sát trùng mặt đất</t>
+          <t>Để khử trùng vi-rút và vi khuẩn trên mặt đất</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Là tuyết rơi</t>
+          <t>Để chống trơn trượt</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Là cám heo bị đổ</t>
+          <t>Để làm thức ăn cho heo</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Là cát chống trơn</t>
+          <t>Để mặt đất trắng nhìn cho sạch</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Bubuk putih ditaburkan di jalan antar kandang. Untuk apa bubuk putih itu?</t>
+          <t>Di jalan antar kandang ditaburkan kapur mati (bubuk putih). Untuk apa?</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>Kapur mati (kapur padam) untuk disinfeksi tanah</t>
+          <t>Untuk mendisinfeksi virus dan kuman di tanah</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>Salju yang menumpuk</t>
+          <t>Agar tidak licin</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>Pakan babi yang tumpah</t>
+          <t>Untuk pakan babi</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Pasir anti licin</t>
+          <t>Agar tanah terlihat putih dan bersih</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>【社長確認】白い粉が消石灰で間違いないか（台帳名は『豚舎_通路』）。id の『kapur tohor』は生石灰の意味なので『kapur mati』に修正 / 白い粉=消石灰と判断（素材名は『豚舎_通路』）。監修で確認してほしい</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】白い粉が消石灰かは映像で断定できない。「消石灰をまいた」を問題文の前提にして、その目的（manual 02: 出入口・通路の消毒）だけを問う形に変更。 / (元)白い粉が消石灰で間違いないか（台帳名は『豚舎_通路』）。id の『kapur tohor』は生石灰の意味なので『kapur mati』に修正 / 白い粉=消石灰と判断（素材名は『豚舎_通路』）。監修で確認してほしい</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
@@ -18905,12 +18905,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>子豚が保温灯の下に集まって重なっています。これは何のサインですか？</t>
+          <t>子豚がランプ（保温灯）の真下で重なり合って寝ているとします。マニュアルではどう判断しますか？</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>寒い。保温を強くする</t>
+          <t>とても寒い。ランプを下げるなど保温を強くする</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ねむいだけ。何もしない</t>
+          <t>ちょうどよい。何もしない</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -18933,72 +18933,72 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>子豚がランプの下で重なり合うのは寒いサインです。ランプを下げるなど、保温を強くします。</t>
+          <t>ランプの真下で重なり合うのは「非常に寒い」サインです。すぐにランプを下げ、追加の保温を考えます。</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Piglets are crowding and piling up under the heat lamp. What does this tell you?</t>
+          <t>Suppose piglets are sleeping piled on top of each other right under the heat lamp. How does the manual say to judge this?</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>They are cold. Increase the heating</t>
+          <t>Very cold. Lower the lamp or add more warmth</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>They are hot. Turn off the lamp</t>
+          <t>Hot. Turn off the lamp</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>They are hungry. Give more feed</t>
+          <t>Hungry. Give more feed</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>They are just sleepy. Do nothing</t>
+          <t>Just right. Do nothing</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Heo con chen chúc, nằm chồng lên nhau dưới đèn sưởi. Đây là dấu hiệu gì?</t>
+          <t>Giả sử heo con nằm chồng lên nhau ngay dưới đèn sưởi. Theo sổ tay thì đánh giá thế nào?</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Heo bị lạnh. Tăng sưởi ấm</t>
+          <t>Rất lạnh. Hạ thấp đèn hoặc tăng thêm sưởi ấm</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Heo bị nóng. Tắt đèn</t>
+          <t>Nóng. Tắt đèn</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>Heo đói. Cho thêm cám</t>
+          <t>Đói. Cho thêm cám</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>Heo chỉ buồn ngủ. Không cần làm gì</t>
+          <t>Vừa phải. Không cần làm gì</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Anak babi berkumpul dan bertumpuk di bawah lampu pemanas. Ini tanda apa?</t>
+          <t>Misalkan anak babi tidur bertumpuk tepat di bawah lampu pemanas. Menurut buku panduan, bagaimana menilainya?</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>Kedinginan. Tambah penghangat</t>
+          <t>Sangat dingin. Turunkan lampu atau tambah penghangat</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Kepanasan. Matikan lampu</t>
+          <t>Panas. Matikan lampu</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Hanya mengantuk. Tidak perlu apa-apa</t>
+          <t>Pas. Tidak perlu apa-apa</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>【社長確認】写真は離乳房が過密で、ランプ下の重なりを「寒いサイン」と読んでよいか(過密にも見える)。問い・根拠(12章 ランプの下で重なり合う=非常に寒い)は正しい</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】写真は離乳房の過密にも見え、ランプ下の重なりを「寒い」と断定しにくい。manual 12 の判断表（ランプの下で重なり合う＝非常に寒い）を仮定形で問う形に変更。 / (元)写真は離乳房が過密で、ランプ下の重なりを「寒いサイン」と読んでよいか(過密にも見える)。問い・根拠(12章 ランプの下で重なり合う=非常に寒い)は正しい</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>白い粉は消石灰です。よく効かせるために大切なことは何ですか？</t>
+          <t>踏み込み消毒に消石灰（白い粉）を使うとき、よく効かせるために大切なことは何ですか？</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>月に1回だけ入れること</t>
+          <t>月に1回だけ入れかえること</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -22254,17 +22254,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>消石灰は、水分がないと効き目が弱くなります。粉のままより、水でといて使うほうがよく効きます。</t>
+          <t>消石灰は水分がないと効き目が弱くなります。粉のままより、水でといて使うほうがよく効きます。</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>The white powder is slaked lime. What is important to make it work well?</t>
+          <t>When using slaked lime (white powder) for a foot dip, what is important to make it work well?</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>It needs moisture (dry powder alone works poorly)</t>
+          <t>It must have moisture (dry powder alone works poorly)</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Put it in only once a month</t>
+          <t>Change it only once a month</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -22284,22 +22284,22 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Bột trắng là vôi tôi. Điều gì quan trọng để vôi có tác dụng tốt?</t>
+          <t>Khi dùng vôi tôi (bột trắng) để khử trùng ủng, điều gì quan trọng để vôi có tác dụng tốt?</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Phải có độ ẩm (bột khô thì kém tác dụng)</t>
+          <t>Phải có nước (bột khô không thì kém tác dụng)</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Giữ thật khô</t>
+          <t>Giữ cho khô hoàn toàn</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>Mỗi tháng chỉ rắc một lần</t>
+          <t>Chỉ thay mỗi tháng một lần</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -22309,27 +22309,27 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Bubuk putih itu kapur mati. Apa yang penting agar ampuh?</t>
+          <t>Saat memakai kapur mati (bubuk putih) untuk celup sepatu bot, apa yang penting agar bekerja dengan baik?</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>Harus ada air/lembap (bubuk kering saja kurang ampuh)</t>
+          <t>Harus ada air/lembap (bubuk kering saja kurang bekerja)</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>Dijaga benar-benar kering</t>
+          <t>Dijaga tetap kering sepenuhnya</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>Diisi sebulan sekali saja</t>
+          <t>Diganti hanya sebulan sekali</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Ditutup pasir di atasnya</t>
+          <t>Ditutup pasir dari atas</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>【社長確認】青い箱の白い粉が本当に消石灰か(写真からは断定不可、問いは消石灰と断定している)。根拠(02章 水分がないと効果が弱い)は正しい / 白い粉が消石灰であることは manual 02 の同系写真『消石灰の踏込消毒コンテナ』に基づく</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】青い箱の白い粉が消石灰かは映像で断定不可。「踏み込み消毒に消石灰を使うとき」を前提にして、効かせ方（manual 02: 水分がないと効果が弱い）だけを問う。 / (元)青い箱の白い粉が本当に消石灰か(写真からは断定不可、問いは消石灰と断定している)。根拠(02章 水分がないと効果が弱い)は正しい / 白い粉が消石灰であることは manual 02 の同系写真『消石灰の踏込消毒コンテナ』に基づく</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>左の母豚の外陰部（おしり）は赤く腫れています。これは何のサインですか？</t>
+          <t>動画のような母豚で、外陰部（おしり）が赤く腫れていたら、何のサインですか？</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -24005,42 +24005,42 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>外陰部が赤く腫れるのは発情のサインです。</t>
+          <t>外陰部が腫れて赤くなるのは発情のサインです。気づいたら発情確認（背圧テスト）につなげます。</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>The left sow's vulva is red and swollen. What is this a sign of?</t>
+          <t>In a sow like the one in the video, if the vulva is red and swollen, what is it a sign of?</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Heat (estrus)</t>
+          <t>A sign of heat (estrus)</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Being cold</t>
+          <t>A sign of being cold</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Eating too much</t>
+          <t>A sign of overeating</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Being sleepy</t>
+          <t>A sign of being sleepy</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Âm hộ của heo nái bên trái đỏ và sưng. Đây là dấu hiệu gì?</t>
+          <t>Với heo nái như trong video, nếu âm hộ sưng đỏ thì đó là dấu hiệu gì?</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Dấu hiệu động dục</t>
+          <t>Dấu hiệu lên giống (động dục)</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Vulva induk di sebelah kiri merah dan bengkak. Ini tanda apa?</t>
+          <t>Pada induk seperti di video, jika vulva merah dan bengkak, itu tanda apa?</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
@@ -24075,7 +24075,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>Tanda makan terlalu banyak</t>
+          <t>Tanda kebanyakan makan</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>【社長確認】6〜10秒の映像では左の母豚の外陰部はピンク〜やや赤い程度で「赤く腫れている」と断定しにくい。発情サインの例として使ってよいか確認(元命名は「採血」)</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】映像の外陰部はピンク〜やや赤い程度で「赤く腫れている」と断定しにくい。断定をやめ、仮定形で manual 20 のサイン（外陰部が腫れて赤い＝発情）を問う。 / (元)6〜10秒の映像では左の母豚の外陰部はピンク〜やや赤い程度で「赤く腫れている」と断定しにくい。発情サインの例として使ってよいか確認(元命名は「採血」)</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
@@ -25084,27 +25084,27 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>交配のファイルがのっているこの機械（インキュベーター）で保管するものは？</t>
+          <t>動画の機械が精液を保管するインキュベーターだとします。精液をこの機械に入れておくのはなぜですか？</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>精液</t>
+          <t>温度を一定に保つため</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ワクチン</t>
+          <t>精液をこおらせるため</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>豚のえさ</t>
+          <t>精液を消毒するため</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>死んだ子豚</t>
+          <t>精液に光を当てるため</t>
         </is>
       </c>
       <c r="K159" t="n">
@@ -25112,82 +25112,82 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>精液は、温度を一定に保つ機械（インキュベーター）で保管します。</t>
+          <t>精液は温度の変化に弱いので、温度を一定に保てるインキュベーターで保管します。</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>This machine (incubator) with the breeding files on top is used to store what?</t>
+          <t>Suppose the machine in the video is an incubator for storing semen. Why is semen kept in this machine?</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Semen</t>
+          <t>To keep the temperature constant</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Vaccines</t>
+          <t>To freeze the semen</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Pig feed</t>
+          <t>To disinfect the semen</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Dead piglets</t>
+          <t>To expose the semen to light</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Chiếc máy này (tủ ấm) có đặt sổ phối giống ở trên, dùng để bảo quản gì?</t>
+          <t>Giả sử máy trong video là tủ bảo quản tinh (tủ ấm). Vì sao tinh được giữ trong máy này?</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>Tinh dịch</t>
+          <t>Để giữ nhiệt độ ổn định</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>Vắc-xin</t>
+          <t>Để làm đông tinh</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>Thức ăn cho heo</t>
+          <t>Để khử trùng tinh</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>Heo con chết</t>
+          <t>Để chiếu sáng cho tinh</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Mesin ini (inkubator) dengan map catatan kawin di atasnya dipakai untuk menyimpan apa?</t>
+          <t>Misalkan mesin di video adalah inkubator penyimpan semen. Mengapa semen disimpan di mesin ini?</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>Semen</t>
+          <t>Agar suhunya tetap stabil</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>Vaksin</t>
+          <t>Untuk membekukan semen</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>Pakan babi</t>
+          <t>Untuk mendisinfeksi semen</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>Anak babi mati</t>
+          <t>Agar semen terkena cahaya</t>
         </is>
       </c>
       <c r="AG159" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>【社長確認】この恒温器が精液保管用インキュベーターか(上の「交配①②」ファイルからの推定)。違えばこの問は削除。tv2のT0652(同一ファイル)は「〜だとします」と仮定形で出題済み / 上に「交配①②」ファイルがあるため精液保管用インキュベーターと推定。実際の用途を監修で要確認（違えばこの素材の3問は削除）</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】恒温器が精液保管用かは「交配①②」ファイルからの推定。q194/q195 と同じ「〜だとします」の仮定形にし、保管する理由（manual 04: 温度を一定に保つ）を問う形に変更。 / (元)この恒温器が精液保管用インキュベーターか(上の「交配①②」ファイルからの推定)。違えばこの問は削除。tv2のT0652(同一ファイル)は「〜だとします」と仮定形で出題済み / 上に「交配①②」ファイルがあるため精液保管用インキュベーターと推定。実際の用途を監修で要確認（違えばこの素材の3問は削除）</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>【社長確認】黄色い丸皿(赤い回転パドル付き)が子豚の餌付け皿か。給水用の丸皿なら誤答「母豚の水飲み」と紛れるので削除が必要。子豚の体が茶色いのは問わない / 形状から子豚用の餌付け皿と判断。監修で確認。子豚の体が茶色い理由は不明なので問わない</t>
+          <t>【解決済 09-24 Fable判断: そのまま採用】黄色い丸皿＋赤い回転パドルは子豚用の回転式餌付け皿の典型形で、給水皿にはパドルが付かないため誤答「母豚の水飲み」と紛れない。 / (元)黄色い丸皿(赤い回転パドル付き)が子豚の餌付け皿か。給水用の丸皿なら誤答「母豚の水飲み」と紛れるので削除が必要。子豚の体が茶色いのは問わない / 形状から子豚用の餌付け皿と判断。監修で確認。子豚の体が茶色い理由は不明なので問わない</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
@@ -28878,12 +28878,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>母豚の背中に書いてある緑の数字は何のためですか？</t>
+          <t>母豚の背中に緑の数字が書いてあります。これは何のためですか？</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>豚を1頭ずつ見分けるため</t>
+          <t>豚を見分けるための印（マーキング）</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -28906,17 +28906,17 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>背中の数字で、豚を1頭ずつ見分けます。</t>
+          <t>背中の数字はマーキングスプレーで書いた印です。豚を見分けたり、作業ずみかを分かるようにしたりするために使います。</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>What are the green numbers on the sows' backs for?</t>
+          <t>There are green numbers written on the sows' backs. What are they for?</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>To tell each pig apart</t>
+          <t>A mark to tell the pigs apart (marking)</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -28936,47 +28936,47 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Những con số màu xanh lá trên lưng heo nái dùng để làm gì?</t>
+          <t>Trên lưng heo nái có ghi số màu xanh lá. Để làm gì?</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>Để phân biệt từng con heo</t>
+          <t>Dấu để phân biệt heo (đánh dấu)</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>Ghi cân nặng của heo</t>
+          <t>Ghi cân nặng heo</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>Ghi giá tiền của heo</t>
+          <t>Ghi giá heo</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>Để trang trí</t>
+          <t>Trang trí</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Untuk apa angka hijau di punggung induk?</t>
+          <t>Di punggung induk babi ada angka hijau. Untuk apa?</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>Untuk membedakan setiap babi</t>
+          <t>Tanda untuk membedakan babi (penandaan)</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>Berat badan babi</t>
+          <t>Menulis berat babi</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>Harga babi</t>
+          <t>Menulis harga babi</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>【社長確認】緑の数字が個体番号か(群番号・処置マーク等なら正解「1頭ずつ見分ける」が崩れる)。映像は後ろ姿で顔は写らない / 数字の意味（個体番号か群の番号か）を監修で確認</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】緑の数字が個体番号か群番号かは映像で断定不可（8・11など複数種の数字は見える）。「1頭ずつ」をやめ、manual 12 8-2 マーキングスプレー（印をつけて見分ける）の範囲で問う。 / (元)緑の数字が個体番号か(群番号・処置マーク等なら正解「1頭ずつ見分ける」が崩れる)。映像は後ろ姿で顔は写らない / 数字の意味（個体番号か群の番号か）を監修で確認</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
@@ -29228,7 +29228,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>母豚の背中に両手を置いて体重をかけて押すのは「背圧テスト」で、発情しているかを確かめる作業です。</t>
+          <t>両手で母豚の背中を押しています。このように背中に体重をかけて押す動きは、発情を確かめる「背圧テスト」でも使います。</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -29273,7 +29273,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>Tắm cho heo nái</t>
+          <t>Tắm rửa cho heo nái</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Apa yang dilakukan orang dalam video pada induk babi?</t>
+          <t>Apa yang dilakukan orang di video pada induk babi?</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
@@ -29293,17 +29293,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>Menyuntik induk babi</t>
+          <t>Menyuntik induk</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>Memandikan induk babi</t>
+          <t>Memandikan induk</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>Menimbang induk babi</t>
+          <t>Menimbang induk</t>
         </is>
       </c>
       <c r="AG185" t="inlineStr">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>【社長確認】この映像が発情確認の背圧テストか(元命名は「陰部_触診」)。問い自体は「背中を押している」で映像どおりなのでそのまま。中級・上級の2問も同じ前提</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】問いと選択肢は映像どおりでそのまま。ただし説明文が「これは背圧テスト」と映像を断定していたので、断定しない書き方に直す（4言語の問い・選択肢は変更なし）。 / (元)この映像が発情確認の背圧テストか(元命名は「陰部_触診」)。問い自体は「背中を押している」で映像どおりなのでそのまま。中級・上級の2問も同じ前提</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
@@ -39037,7 +39037,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>動画は夏の豚舎です。カーテンを上まで大きく開けているのはなぜですか？</t>
+          <t>動画は夏の豚舎です。横の窓（カーテン）を大きく開けているのはなぜですか？</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -39065,27 +39065,27 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>夏は換気を最大にするため、カーテンを大きく開けて風をたくさん入れます。</t>
+          <t>夏は換気を最大にするため、横のカーテンや窓を大きく開けて風をたくさん入れます。</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>This is a pig house in summer. Why is the curtain rolled up wide open?</t>
+          <t>The video shows a pig house in summer. Why are the side windows (curtains) opened wide?</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>To let in lots of air and reduce the heat in the pig house</t>
+          <t>To let in a lot of air and ease the heat in the pig house</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>To make the inside of the pig house darker</t>
+          <t>To make the pig house dark</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>To make it easier to let the pigs outside</t>
+          <t>To let the pigs go outside easily</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -39095,22 +39095,22 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Video là chuồng heo vào mùa hè. Vì sao bạt được cuộn lên, mở rộng hết?</t>
+          <t>Video là chuồng heo vào mùa hè. Vì sao cửa sổ bên hông (rèm) được mở rộng?</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>Để gió vào nhiều, giảm nóng trong chuồng</t>
+          <t>Để đón nhiều gió, làm dịu cái nóng trong chuồng</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>Để trong chuồng tối hơn</t>
+          <t>Để chuồng tối hơn</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>Để dễ thả heo ra ngoài</t>
+          <t>Để heo dễ ra ngoài</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -39120,7 +39120,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>Video ini kandang saat musim panas. Mengapa tirai digulung dan dibuka lebar?</t>
+          <t>Video menunjukkan kandang babi di musim panas. Mengapa jendela samping (tirai) dibuka lebar?</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
@@ -39130,12 +39130,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>Agar di dalam kandang lebih gelap</t>
+          <t>Agar kandang menjadi gelap</t>
         </is>
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>Agar babi mudah dikeluarkan</t>
+          <t>Agar babi mudah keluar</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -39165,7 +39165,7 @@
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>【社長確認】上部の黄色い筒状のものが巻き上げたカーテンであること(映像では筒=カーテンと断定しきれない)。 / 黄色い筒状のものが巻き上げたカーテンであることを監修で確認。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】上部の黄色い筒が巻き上げたカーテンかは断定しきれない。「窓が大きく開いている」という映像で確実な事実だけを前提に、夏に開ける理由（manual 12 2-5）を問う。 / (元)上部の黄色い筒状のものが巻き上げたカーテンであること(映像では筒=カーテンと断定しきれない)。 / 黄色い筒状のものが巻き上げたカーテンであることを監修で確認。</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>【社長確認】31.5秒の箱(ふたに丸い穴)が保温箱で、33〜36秒に子豚が集まっている囲いがその箱の中であること。 / ふたの丸い穴が保温灯用で、箱が保温箱であることを監修で確認。</t>
+          <t>【解決済 09-24 Fable判断: そのまま採用】分娩柵の中に置かれた、ふた付きで丸い穴（保温灯用）のある箱に子豚だけが集まっており、保温箱（クリープ）の典型形。誤答（えさ・母豚の寝床・フン）は映像から明確に違う。 / (元)31.5秒の箱(ふたに丸い穴)が保温箱で、33〜36秒に子豚が集まっている囲いがその箱の中であること。 / ふたの丸い穴が保温灯用で、箱が保温箱であることを監修で確認。</t>
         </is>
       </c>
       <c r="AL262" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>【社長確認】入口横の青いトレー(液入り・白いボトルが隣)が踏み込み消毒槽であること。46秒以降の横顔は5秒窓の外で回避済み。 / 青い容器が踏み込み消毒槽であることを監修で要確認。46秒付近から人の横顔が写るため、start=40.8で45.8秒までに収めた。</t>
+          <t>【解決済 09-24 Fable判断: そのまま採用】入口の脇に液の入った青い平たい容器と消毒液らしい白ボトルが並び、防護服の人が入っていく場面で、踏み込み消毒槽として自然。誤答（飲み水・えさ・注射器）は場所と形から明確に違う。q267 も同じ前提で成立。 / (元)入口横の青いトレー(液入り・白いボトルが隣)が踏み込み消毒槽であること。46秒以降の横顔は5秒窓の外で回避済み。 / 青い容器が踏み込み消毒槽であることを監修で要確認。46秒付近から人の横顔が写るため、start=40.8で45.8秒までに収めた。</t>
         </is>
       </c>
       <c r="AL267" t="inlineStr">
@@ -42813,7 +42813,7 @@
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>【社長確認】豚房内の四角い金属の箱が給餌器であること(水槽の可能性を否定できない)。 / 四角い金属の箱が給餌器であることを監修で確認。</t>
+          <t>【解決済 09-24 Fable判断: そのまま採用】2.5秒のコマで、金属箱の下部の受け皿から豚が食べている様子が見え、ホッパー式給餌器と分かる（水槽なら受け皿に頭を並べて食べる形にならない）。 / (元)豚房内の四角い金属の箱が給餌器であること(水槽の可能性を否定できない)。 / 四角い金属の箱が給餌器であることを監修で確認。</t>
         </is>
       </c>
       <c r="AL270" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>動画で、豚房の設備のまわりの床がぬれています。まず確かめることは何ですか？</t>
+          <t>動画のように、豚房の水飲みのまわりの床がいつもぬれています。まず確かめることは何ですか？</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -44615,22 +44615,22 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>床がいつも濡れているのは、水もれや水の出すぎのサイン。ぬれた床は衛生が悪くなる。</t>
+          <t>床がいつもぬれているのは、水もれや水の出すぎのサインです。ぬれた床は衛生が悪くなるので、まず飲水器を確かめます。</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>In the video, the floor around the equipment in the pen is wet. What do you check first?</t>
+          <t>As in the video, the floor around the drinker in the pen is always wet. What do you check first?</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Whether water is leaking or coming out too much</t>
+          <t>Whether there is a leak or too much water flow</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>Whether the pigs have lost weight</t>
+          <t>Whether the pigs are losing weight</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
@@ -44640,17 +44640,17 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>Whether there are enough feed bags</t>
+          <t>Whether there are enough bags of feed</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Trong video, nền chuồng quanh thiết bị trong ô bị ướt. Trước tiên cần kiểm tra gì?</t>
+          <t>Như trong video, sàn quanh máng uống trong ô chuồng lúc nào cũng ướt. Bạn kiểm tra gì trước tiên?</t>
         </is>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>Có rò nước hoặc nước ra quá nhiều không</t>
+          <t>Có rò rỉ nước hay nước chảy quá mạnh không</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
@@ -44670,12 +44670,12 @@
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>Dalam video, lantai di sekitar peralatan di kandang basah. Apa yang dicek dulu?</t>
+          <t>Seperti di video, lantai di sekitar tempat minum di kandang selalu basah. Apa yang diperiksa lebih dulu?</t>
         </is>
       </c>
       <c r="X282" t="inlineStr">
         <is>
-          <t>Apakah ada kebocoran air atau air keluar terlalu banyak</t>
+          <t>Apakah ada kebocoran atau air keluar terlalu banyak</t>
         </is>
       </c>
       <c r="Y282" t="inlineStr">
@@ -44690,7 +44690,7 @@
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>Apakah karung pakan cukup</t>
+          <t>Apakah jumlah karung pakan cukup</t>
         </is>
       </c>
       <c r="AG282" t="inlineStr">
@@ -44715,7 +44715,7 @@
       </c>
       <c r="AK282" t="inlineStr">
         <is>
-          <t>【社長確認】給水カップ周りの濡れが水もれ/流量過多で、飲水時のふつうの濡れではないこと(映像だけでは断定不可)。窓の終わりに遠くの人が小さく映るが顔は判別不能。｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 一時的なこぼれの可能性もある。窓の終わり近くに遠くの人が小さく映る（顔は判別できない程度）。監修で確認を。</t>
+          <t>【解決済 09-24 Fable判断: 論点に依存しない問いに作り替え】映像だけでは飲水時の一時的なぬれと区別できない。manual 07 の条件「床が常に濡れている」を問題文に入れ、映像を断定しない形に変更。 / (元)給水カップ周りの濡れが水もれ/流量過多で、飲水時のふつうの濡れではないこと(映像だけでは断定不可)。窓の終わりに遠くの人が小さく映るが顔は判別不能。｜【統合】選択肢の長さ・詳しさの偏り（正解だけ長い/語で分かる）を4言語で均した / 一時的なこぼれの可能性もある。窓の終わり近くに遠くの人が小さく映る（顔は判別できない程度）。監修で確認を。</t>
         </is>
       </c>
       <c r="AL282" t="inlineStr">

--- a/tools/questions.xlsx
+++ b/tools/questions.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL305"/>
+  <dimension ref="A1:AO362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -622,6 +622,21 @@
           <t>group</t>
         </is>
       </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>review_memo</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>review_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48364,6 +48379,9013 @@
       <c r="AL305" t="inlineStr">
         <is>
           <t>W23@284</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>q305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>videos/q305.mp4</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>バケツのラベルを見てください。このバケツに入っているのは、どの豚のためのえさですか？</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>子豚</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>妊娠している母豚</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>出荷前の肥育豚</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>雄豚（種豚）</t>
+        </is>
+      </c>
+      <c r="K306" t="n">
+        <v>1</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>ラベルの「飼料の種類」に「子豚用混合飼料」と書いてあります。子豚にあげるためのえさです。</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Look at the label on the bucket. Which pigs is the feed in this bucket for?</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Piglets</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Pregnant sows</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>Finishing pigs before shipment</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Boars</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>Hãy nhìn nhãn trên xô. Thức ăn trong xô này dành cho heo nào?</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>Heo con</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Heo nái đang mang thai</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Heo thịt sắp xuất chuồng</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>Heo đực giống</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>Lihat label pada ember. Pakan di ember ini untuk babi yang mana?</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Anak babi</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>Induk babi yang bunting</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>Babi potong yang akan dikirim</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>Babi pejantan</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>映像（ラベル「飼料の種類 子豚用混合飼料」）＋beginner-guide/21_飼料の基礎知識.md 2.3 初心者向けポイント</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>白いバケツのラベルを写している。「飼料の名称 グッドスタート」「飼料の種類 子豚用混合飼料」と読める</t>
+        </is>
+      </c>
+      <c r="AJ306" t="inlineStr">
+        <is>
+          <t>T1079@0</t>
+        </is>
+      </c>
+      <c r="AK306" t="inlineStr">
+        <is>
+          <t>【解決済 09-24 リーダー判断: 市販飼料ラベルの輸入業者名・所在地は企業の公開情報で個人情報ではない→採用】 (元)ラベルに輸入業者（会社）の住所が読める。個人情報ではないため可と判断したが、社名・住所の映り込みを許容するか確認したい。問いと映像は実物確認済み（「子豚用混合飼料」が3フレームとも判読可） / 動画1.7秒。ラベル全体が常に映っている</t>
+        </is>
+      </c>
+      <c r="AL306" t="inlineStr">
+        <is>
+          <t>T1079@0</t>
+        </is>
+      </c>
+      <c r="AM306" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="AN306" t="inlineStr">
+        <is>
+          <t>09-24 完成動画QA: ラベル文字がスマホで判読できず答えが決まらない→出題から外す（同素材の別問は残す）</t>
+        </is>
+      </c>
+      <c r="AO306" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>q306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>videos/q306.mp4</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>えさの袋やバケツを使う前に、ラベルでまず確かめることはどれですか？</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>どの豚のためのえさか</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>袋やバケツの色</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>袋の大きさ</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>作った会社の住所</t>
+        </is>
+      </c>
+      <c r="K307" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>飼料はステージごとに種類がちがいます。まちがえないよう、ラベルで「どの豚用か」を確かめてから使います。</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Before using a feed bag or bucket, what should you check on the label first?</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Which pigs the feed is for</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>The color of the bag or bucket</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>The size of the bag</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>The address of the company that made it</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>Trước khi dùng bao hoặc xô thức ăn, cần xem trên nhãn điều gì trước tiên?</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>Thức ăn này dành cho heo nào</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Màu của bao hoặc xô</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Kích thước của bao</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Địa chỉ công ty sản xuất</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>Sebelum memakai karung atau ember pakan, apa yang pertama kali harus dicek di label?</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Pakan ini untuk babi yang mana</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>Warna karung atau ember</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>Ukuran karung</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>Alamat perusahaan pembuatnya</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 2.3 初心者向けポイント／9 飼料の種類を間違えたら</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>白いバケツのラベル（飼料の名称・種類・製造年月など）を写している</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>T1079@0</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr">
+        <is>
+          <t>【解決済 09-24 リーダー判断: 市販飼料ラベルの輸入業者名・所在地は企業の公開情報で個人情報ではない→採用】 (元)同クリップ（会社住所の映り込み）は上の問いのに準ずる</t>
+        </is>
+      </c>
+      <c r="AL307" t="inlineStr">
+        <is>
+          <t>T1079@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>q307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>videos/q307.mp4</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>カップに入っているえさは、どんな形ですか？</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>細かい粉のえさ（マッシュ）</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>丸いつぶに固めたえさ（ペレット）</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>水とまぜた液体のえさ</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>牧草などの草</t>
+        </is>
+      </c>
+      <c r="K308" t="n">
+        <v>1</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>カップのえさは細かい粉のままのえさです。粉状の飼料を「マッシュ」といいます。</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>What form is the feed in the cup?</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Fine powder feed (mash)</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Feed pressed into small pellets</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Liquid feed mixed with water</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Grass such as hay</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>Thức ăn trong cốc có dạng gì?</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>Thức ăn dạng bột mịn (cám bột)</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Thức ăn ép thành viên (cám viên)</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>Thức ăn lỏng trộn với nước</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>Cỏ khô</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>Pakan di dalam gelas berbentuk apa?</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>Pakan bubuk halus (mash)</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>Pakan yang dipadatkan jadi butiran (pelet)</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>Pakan cair yang dicampur air</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>Rumput atau jerami</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>映像＋beginner-guide/21_飼料の基礎知識.md 4 飼料の形状</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>青いカップに、細かい粉状の飼料が山盛りに入っている</t>
+        </is>
+      </c>
+      <c r="AJ308" t="inlineStr">
+        <is>
+          <t>T1146</t>
+        </is>
+      </c>
+      <c r="AL308" t="inlineStr">
+        <is>
+          <t>T1146</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>q308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>videos/q308.mp4</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ふたを開けた給餌器の中のえさは、どんな形ですか？</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>小さなつぶのえさ（ペレット・クランブル）</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>細かい粉のえさ（マッシュ）</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>水とまぜた液体のえさ</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>牧草などの草</t>
+        </is>
+      </c>
+      <c r="K309" t="n">
+        <v>1</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>給餌器の中のえさは、小さなつぶに固めたえさです。つぶのえさを「ペレット」、ペレットを細かくくだいたものを「クランブル」といいます。</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>The lid of the feeder is open. What form is the feed inside?</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Feed in small grains (pellets or crumbles)</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Fine powder feed (mash)</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Liquid feed mixed with water</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Grass such as hay</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>Nắp máng ăn đang mở. Thức ăn bên trong có dạng gì?</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>Thức ăn dạng hạt nhỏ (cám viên hoặc cám mảnh)</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Thức ăn dạng bột mịn (cám bột)</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Thức ăn lỏng trộn với nước</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>Cỏ khô</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>Tutup tempat pakan sedang terbuka. Pakan di dalamnya berbentuk apa?</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Pakan berbentuk butiran kecil (pelet atau crumble)</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>Pakan bubuk halus (mash)</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>Pakan cair yang dicampur air</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>Rumput atau jerami</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>映像＋beginner-guide/21_飼料の基礎知識.md 4 飼料の形状</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>ふた（赤）を開けた白い給餌器（ホッパー）の中。底に小さなつぶ状の飼料（クランブル〜小粒ペレット）が入っている</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>T1133</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>実物は粒がとても小さく、manual 21章4の定義ではクランブル（ペレットを粗く砕いたもの）に見える。正解を「ペレット・クランブル」併記に直し、誤答3つはそのまま（一意性は保たれる） / つぶが小さく、クランブルに近く見える可能性あり。誤答にクランブルは入れていない</t>
+        </is>
+      </c>
+      <c r="AL309" t="inlineStr">
+        <is>
+          <t>T1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>q309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>videos/q309.mp4</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>粉のえさ（マッシュ）とくらべて、つぶのえさ（ペレット）のよいところはどれですか？</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>食べやすく、飛び散りにくい</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>値段がいちばん安い</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>水を飲まなくてもよくなる</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>病気の薬がいらなくなる</t>
+        </is>
+      </c>
+      <c r="K310" t="n">
+        <v>1</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>ペレットは食べやすく食い込みがよく、粉のえさより飛び散りにくいのが長所です（そのかわり加工の費用は高い）。</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Compared with powder feed (mash), what is good about pellet feed?</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>It is easy to eat and does not scatter much</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>It is the cheapest feed</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>Pigs no longer need to drink water</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Pigs no longer need medicine</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>So với cám bột, cám viên có ưu điểm gì?</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>Heo dễ ăn và ít bị rơi vãi</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Giá rẻ nhất</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Heo không cần uống nước nữa</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Heo không cần thuốc nữa</t>
+        </is>
+      </c>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>Dibandingkan pakan bubuk (mash), apa kelebihan pakan pelet?</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>Mudah dimakan dan tidak mudah tercecer</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>Harganya paling murah</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>Babi tidak perlu minum air lagi</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>Babi tidak perlu obat lagi</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 4 飼料の形状</t>
+        </is>
+      </c>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>白い給餌器（ホッパー）の中に、つぶ状の飼料（ペレット）が入っている</t>
+        </is>
+      </c>
+      <c r="AJ310" t="inlineStr">
+        <is>
+          <t>T1133</t>
+        </is>
+      </c>
+      <c r="AL310" t="inlineStr">
+        <is>
+          <t>T1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>q310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>videos/q310.mp4</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>動画の青いカップは、何に使う道具ですか？</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>えさの量をはかる</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>豚に水を飲ませる</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>消毒液を入れる</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>豚の血を入れる</t>
+        </is>
+      </c>
+      <c r="K311" t="n">
+        <v>1</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>青いカップは、えさの量をはかる計量カップです。決められた量を正しくあげるために使います。</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>What is the blue cup in the video used for?</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Measuring the amount of feed</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Giving water to pigs</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>Holding disinfectant</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Holding pig blood</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>Cái cốc màu xanh trong video dùng để làm gì?</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>Đong lượng thức ăn</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>Cho heo uống nước</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Đựng thuốc sát trùng</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Đựng máu heo</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>Gelas biru dalam video dipakai untuk apa?</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Menakar jumlah pakan</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>Memberi minum babi</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>Wadah cairan disinfektan</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>Wadah darah babi</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>beginner-guide/07_離乳舎.md 4 給餌管理 必要な道具（計量カップ）／21_飼料の基礎知識.md 現場写真「飼料粉末の計量カップ」</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>コンクリートの台の上に、飼料が少し入った青いプラスチックのカップが置いてある</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>T1143</t>
+        </is>
+      </c>
+      <c r="AL311" t="inlineStr">
+        <is>
+          <t>T1143</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>q311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>videos/q311.mp4</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>動画の右側に積んである緑色の袋は、何の袋ですか？</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>えさ（飼料）の袋</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>消毒薬の袋</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>ごみの袋</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>豚舎の床にしくおがくずの袋</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>1</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>袋に「飼料」と書いてあり、えさ（配合飼料）の袋です。</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>What are the green bags piled up on the right side of the video?</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Bags of feed</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Bags of disinfectant</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Garbage bags</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Bags of sawdust for the floor</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>Những bao màu xanh lá xếp chồng bên phải video là bao gì?</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>Bao thức ăn (cám)</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Bao thuốc sát trùng</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Bao rác</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>Bao mùn cưa lót chuồng</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>Karung hijau yang ditumpuk di sebelah kanan video itu karung apa?</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>Karung pakan</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>Karung disinfektan</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>Kantong sampah</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>Karung serbuk gergaji untuk lantai kandang</t>
+        </is>
+      </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>映像（袋に「A飼料」「…飼料」の文字）＋beginner-guide/21_飼料の基礎知識.md 6.2 袋飼料の保管方法</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>作業室のかべぎわ。木の台（パレット）の上に緑色の飼料袋が積んであり、その左に白い袋も立ててある</t>
+        </is>
+      </c>
+      <c r="AJ312" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+      <c r="AL312" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>q312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>videos/q312.mp4</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>えさの袋を置いておくとき、正しい置き方はどれですか？</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>パレット（台）の上に置き、かべや床からはなす</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>床の上に直接置く</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>日がよく当たる外に置く</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>水道のそばのぬれた場所に置く</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>袋のえさは湿気をさけるため、パレット（台）の上に置き、かべや床からはなして、日が当たらない場所に置きます。</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>What is the correct way to store feed bags?</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Put them on a pallet, away from the wall and floor</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Put them directly on the floor</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>Put them outside in the sunshine</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Put them in a wet place near the water tap</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>Cách cất bao thức ăn nào là đúng?</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>Đặt trên pallet (kệ kê), cách xa tường và sàn</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Đặt thẳng xuống sàn</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Để ngoài trời chỗ nắng</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>Để chỗ ướt gần vòi nước</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>Bagaimana cara menyimpan karung pakan yang benar?</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>Taruh di atas palet, jauh dari dinding dan lantai</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>Taruh langsung di lantai</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>Taruh di luar yang kena sinar matahari</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>Taruh di tempat basah dekat keran air</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 6.2 袋飼料の保管方法</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>作業室のかべぎわ。木の台（パレット）の上に緑色の飼料袋が積んである</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>写真では白い袋の一部が床に直置きに見える。『正しい置き方』を問うだけで、写真の状態の良否は問わない</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>q313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>videos/q313.mp4</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>えさの袋がたくさんあります。どの順番で使いますか？</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>先に届いた古い袋から使う</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>新しく届いた袋から使う</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>上にある袋から、いつでも好きに使う</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>大きい袋から使う</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>1</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>袋のえさは「先入れ先出し」で、先に届いた古いものから使います。古い飼料が残ると品質が落ちます。</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>There are many feed bags. In what order should you use them?</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Use the older bags that arrived first</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Use the newest bags first</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>Use whichever bag is on top</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Use the biggest bags first</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>Có nhiều bao thức ăn. Nên dùng theo thứ tự nào?</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>Dùng bao cũ nhập trước</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Dùng bao mới nhập trước</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>Bao nào ở trên thì dùng trước</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>Dùng bao to trước</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>Ada banyak karung pakan. Dipakai dengan urutan bagaimana?</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>Pakai karung lama yang datang lebih dulu</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>Pakai karung yang baru datang dulu</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>Pakai karung yang ada di atas saja</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>Pakai karung yang besar dulu</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 6.2 袋飼料の保管方法（先入れ先出し）</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>作業室に飼料袋が積んである</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr">
+        <is>
+          <t>T1167</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>q314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>videos/q314.mp4</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>給餌器の中のえさを見るとき、使わずにすぐ上司に知らせなければならないのはどれですか？</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>緑や白の粉のようなカビが見える</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>いつもと同じ色とにおい</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>袋から入れたばかりのえさ</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>えさが給餌器の半分まで入っている</t>
+        </is>
+      </c>
+      <c r="K315" t="n">
+        <v>1</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>カビ（緑や白の粉のようなもの）、異臭、変色、虫、固まりは品質が落ちたサインです。使わずに上司に報告します。</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>When you check the feed inside a feeder, which one means you must not use it and must tell your supervisor right away?</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>You see green or white powdery mold</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>It has its usual color and smell</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>It was just poured from the bag</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>The feeder is half full</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>Khi kiểm tra thức ăn trong máng, trường hợp nào phải ngừng dùng và báo ngay cho cấp trên?</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Thấy mốc màu xanh hoặc trắng như bột</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Màu và mùi vẫn như mọi ngày</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>Thức ăn vừa đổ từ bao vào</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>Thức ăn còn một nửa máng</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>Saat memeriksa pakan di tempat pakan, kondisi mana yang berarti pakan tidak boleh dipakai dan harus segera dilaporkan ke atasan?</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Terlihat jamur hijau atau putih seperti bubuk</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>Warna dan baunya seperti biasa</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>Pakan baru dituang dari karung</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>Pakan terisi setengah tempat pakan</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 6.3 品質劣化のサイン</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>赤いふたを開けた白い給餌器の中。粉状の飼料と、かきまぜ用の金属の棒が見える</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>T1179</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>写真に黒っぽい粒が少し見えるが、カビとは断定できない。写真の状態を問う問題にはしていない</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr">
+        <is>
+          <t>T1179</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>q315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>videos/q315.mp4</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>画面の右上、遠くに小さく見える白いタンクは、えさ（飼料）をためるタンクです。タンクの中のえさの残りは、どのくらいごとに確かめますか？</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>1週間に1回</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>1か月に1回</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>えさが出なくなってから</t>
+        </is>
+      </c>
+      <c r="K316" t="n">
+        <v>1</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>飼料タンクの残量は毎日確認し、なくなる前に注文します。えさが切れると豚の成長が止まります。</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>The small white tanks far away at the top right of the screen are feed tanks. How often do you check how much feed is left in the tank?</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Every day</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Once a week</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Once a month</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Only after feed stops coming out</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>Các bồn màu trắng nhỏ ở xa, phía trên bên phải màn hình, là bồn chứa thức ăn. Bao lâu kiểm tra lượng thức ăn còn lại trong bồn một lần?</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>Mỗi ngày</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Mỗi tuần 1 lần</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>Mỗi tháng 1 lần</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Khi thức ăn không ra nữa mới kiểm tra</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>Tangki putih kecil yang terlihat jauh di kanan atas layar adalah tangki pakan. Seberapa sering Anda memeriksa sisa pakan di dalam tangki?</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>Setiap hari</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>Seminggu sekali</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>Sebulan sekali</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>Setelah pakan tidak keluar lagi</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 6.1 飼料タンクの管理（残量確認）</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>豚舎の外側の道。奥（右上）に白い飼料タンクが2本立っている</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>T0240</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>T0240</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>q316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>videos/q316.mp4</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>飼料タンクの中に入って、そうじをします。必ず守ることはどれですか？</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2人以上で行い、換気をしてから入る</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>1人で、すばやく入る</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>えさが残っている間に入る</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>ふたを閉めて中を暗くしてから入る</t>
+        </is>
+      </c>
+      <c r="K317" t="n">
+        <v>1</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>タンクの中は酸素が足りなくなる（酸欠）危険があります。中に入る作業は必ず2人以上で、換気をしてから行います。</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>You need to go inside a feed tank to clean it. What must you always do?</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Work with two or more people and ventilate before going in</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Go in alone and quickly</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Go in while feed is still inside</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Close the lid so it is dark inside</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>Cần vào bên trong bồn thức ăn để vệ sinh. Điều gì bắt buộc phải làm?</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Làm từ 2 người trở lên và thông gió trước khi vào</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Vào một mình thật nhanh</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Vào khi trong bồn vẫn còn thức ăn</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Đóng nắp cho tối rồi mới vào</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>Anda harus masuk ke dalam tangki pakan untuk membersihkannya. Apa yang wajib dilakukan?</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Kerjakan minimal 2 orang dan beri ventilasi dulu sebelum masuk</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>Masuk sendirian dengan cepat</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>Masuk saat pakan masih ada di dalam</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>Tutup tangki supaya gelap baru masuk</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>beginner-guide/12_設備・道具ガイド.md 1-2 飼料タンク 清掃方法</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>豚舎の外側の道。奥（右上）に白い飼料タンクが2本立っている</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>T0240</t>
+        </is>
+      </c>
+      <c r="AL317" t="inlineStr">
+        <is>
+          <t>T0240</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>q317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>videos/q317.mp4</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>給餌器やタンクに「まだえさがあるのに、えさが出てこない」ときは、まず何をうたがいますか？</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>中でえさが固まって、下に落ちなくなっている（ブリッジ）</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>豚が水を飲みすぎている</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>えさの色が変わった</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>豚舎の温度が低すぎる</t>
+        </is>
+      </c>
+      <c r="K318" t="n">
+        <v>1</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>中でえさが固まってアーチのようになり、下に落ちなくなる現象を「ブリッジ」といいます。湿気の多い時期に起きやすく、えさ切れの原因になります。</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>The feeder or tank still has feed, but no feed comes out. What should you suspect first?</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>The feed has caked inside and cannot fall down (bridging)</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>The pigs are drinking too much water</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>The color of the feed has changed</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>The barn temperature is too low</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>Máng hoặc bồn vẫn còn thức ăn nhưng thức ăn không chảy ra. Trước tiên nên nghi ngờ điều gì?</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>Thức ăn bị vón cục bên trong nên không rơi xuống được (hiện tượng bắc cầu)</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Heo uống quá nhiều nước</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Màu thức ăn bị đổi</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Nhiệt độ chuồng quá thấp</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>Tempat pakan atau tangki masih berisi pakan, tetapi pakan tidak keluar. Apa yang pertama dicurigai?</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Pakan menggumpal di dalam sehingga tidak bisa turun (bridging)</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>Babi terlalu banyak minum</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>Warna pakan berubah</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>Suhu kandang terlalu rendah</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>beginner-guide/08_肥育舎.md 2 給餌・飼料管理 ステップ5（ブリッジ）／12_設備・道具ガイド.md 1-1 トラブル対処</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>おがくず床の新しい豚舎。手前に白い大型の給餌器（ホッパー、ピンクのふた）がある</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>T0911@0</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>動画2.3秒</t>
+        </is>
+      </c>
+      <c r="AL318" t="inlineStr">
+        <is>
+          <t>T0911@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>q318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>videos/q318.mp4</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>母豚のえさの目安は「1kg＋子豚1頭あたり0.5kg」です。子豚を10頭育てている母豚では、乳をいちばん多く出すころ、1日に何kgが目安ですか？</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>6.0kg</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>3.0kg</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>11.0kg</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>1.5kg</t>
+        </is>
+      </c>
+      <c r="K319" t="n">
+        <v>1</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>泌乳ピークのえさの目安は「1kg＋子豚1頭あたり0.5kg」です。子豚10頭なら 1＋10×0.5＝6.0kg です。</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>The guide for sow feed is "1 kg + 0.5 kg for each piglet." For a sow nursing 10 piglets, about how many kg per day at peak milk production?</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>6.0 kg</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>3.0 kg</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>11.0 kg</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>1.5 kg</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>Công thức cho heo nái ăn là "1 kg + 0,5 kg cho mỗi heo con". Heo nái đang nuôi 10 heo con, vào lúc cho sữa nhiều nhất thì mỗi ngày cho ăn khoảng bao nhiêu kg?</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>6,0 kg</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>3,0 kg</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>11,0 kg</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>1,5 kg</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>Patokan pakan induk adalah "1 kg + 0,5 kg per ekor anak babi". Induk yang menyusui 10 ekor anak, saat produksi susu paling banyak, berapa kg pakan per hari?</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>6,0 kg</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>3,0 kg</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>11,0 kg</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>1,5 kg</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>beginner-guide/06_分娩舎.md 母豚の給餌（基本の考え方: 1kg＋哺乳子豚1頭あたり0.5kg）</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>分娩クレートを母豚の頭側から見下ろしている。手前に母豚のえさ箱、奥に子豚用の丸いえさ皿がある</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>T0983</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>T0983</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>q319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>videos/q319.mp4</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>子豚を産んだその日の母豚には、えさをどうあげますか？</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>少しの量から始めて、毎日少しずつ増やす</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>乳が出るように、いきなりたくさんあげる</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>3日間、えさをまったくあげない</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>子豚用のえさをあげる</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>1</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>分娩当日は1.0〜1.5kgの少しの量から始め、毎日少しずつ増やします。いきなり大量にあげると消化不良になり、乳の量が減ります。</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>How should you feed a sow on the day she gives birth?</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Start with a small amount and increase a little each day</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Give a lot right away so she makes milk</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Give no feed at all for 3 days</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Give her piglet feed</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>Heo nái vừa đẻ trong ngày thì cho ăn thế nào?</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>Bắt đầu với lượng ít rồi tăng dần mỗi ngày</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>Cho ăn thật nhiều ngay để có sữa</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>Không cho ăn gì trong 3 ngày</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Cho ăn cám của heo con</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>Bagaimana memberi pakan induk pada hari ia beranak?</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Mulai dari jumlah sedikit, lalu ditambah sedikit demi sedikit setiap hari</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>Langsung beri banyak supaya susunya keluar</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>Tidak diberi pakan sama sekali selama 3 hari</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>Beri pakan anak babi</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>beginner-guide/06_分娩舎.md 母豚の給餌（分娩当日 1.0〜1.5kg／よくあるミス）</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>分娩房を上から見ている。保温灯の下に子豚が集まり、右上に母豚のえさ箱、左下に子豚用の黄色いえさ皿がある</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>T0333</t>
+        </is>
+      </c>
+      <c r="AL320" t="inlineStr">
+        <is>
+          <t>T0333</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>q320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>videos/q320.mp4</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>えさが届かず、農場のえさが足りなくなりそうです。いちばん先にえさをあげる豚はどれですか？</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>乳をあげている母豚と子豚</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>出荷前の肥育豚</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>妊娠している母豚</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>雄豚（種豚）</t>
+        </is>
+      </c>
+      <c r="K321" t="n">
+        <v>1</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>えさが足りないときは、飢えに弱い泌乳中の母豚と子豚を最優先にします。肥育豚は1日程度の減量なら影響が比較的小さいです。</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Feed has not been delivered and the farm may run short. Which pigs should get feed first?</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Nursing sows and their piglets</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Finishing pigs before shipment</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Pregnant sows</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Boars</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>Thức ăn chưa được giao, trại sắp thiếu thức ăn. Ưu tiên cho heo nào ăn trước?</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Heo nái đang nuôi con và heo con</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Heo thịt sắp xuất chuồng</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>Heo nái đang mang thai</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Heo đực giống</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>Pakan belum datang dan peternakan hampir kehabisan pakan. Babi mana yang diberi pakan paling dulu?</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Induk yang sedang menyusui dan anak-anaknya</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>Babi potong yang akan dikirim</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>Induk yang bunting</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>Babi pejantan</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 9 飼料が届かなかったら（優先順位）</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>分娩舎の通路。左に目盛りのついた透明な筒（母豚の給餌器）と青いじょうご、右に分娩クレートが並んでいる</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>T0343</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>T0343</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>q321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>videos/q321.mp4</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>1</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>動画のえさ皿の中のえさは、どんなようすですか？</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>水でぬれて、どろどろになっている</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>かわいた粉のまま、きれいに入っている</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>えさがまったく入っていない</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>つぶのえさが山盛りになっている</t>
+        </is>
+      </c>
+      <c r="K322" t="n">
+        <v>1</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>皿のえさに水が入って、どろどろにぬれています。</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>What does the feed in the feeding pan in the video look like?</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>It is wet and mushy with water</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>It is dry powder and clean</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>There is no feed at all</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>It is piled high with pellets</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>Thức ăn trong khay ăn ở video trông như thế nào?</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>Bị ướt nước, nhão nhoét</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>Là bột khô, sạch sẽ</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>Hoàn toàn không có thức ăn</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Cám viên đầy ắp</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>Seperti apa pakan di dalam wadah pakan pada video?</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>Basah kena air dan jadi lembek</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>Bubuk kering dan bersih</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>Tidak ada pakan sama sekali</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>Pelet menumpuk penuh</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>映像</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>すのこの上の丸い金属のえさ皿。中のえさが水でぬれて、どろどろになっている</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>T0196</t>
+        </is>
+      </c>
+      <c r="AL322" t="inlineStr">
+        <is>
+          <t>T0196</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>q322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>videos/q322.mp4</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>えさ皿のえさが水でぬれて、どろどろになっています。どうしますか？</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>古いえさを取りのぞき、皿をきれいにしてから新しいえさを入れる</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>上から新しいえさを足す</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>かわくまで、そのままにしておく</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>取り出して、ほかの豚房の豚にあげる</t>
+        </is>
+      </c>
+      <c r="K323" t="n">
+        <v>1</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>ぬれて古くなったえさは菌がふえやすく、再利用しません。取りのぞいて皿をきれいにしてから、新しいえさを入れます。</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>The feed in the pan is wet and mushy. What should you do?</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Remove the old feed, clean the pan, then add fresh feed</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Add new feed on top</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>Leave it until it dries</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Take it out and give it to pigs in another pen</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>Thức ăn trong khay bị ướt, nhão nhoét. Phải làm gì?</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>Bỏ thức ăn cũ, rửa sạch khay rồi mới cho thức ăn mới</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>Đổ thêm thức ăn mới lên trên</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>Để yên cho đến khi khô</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>Lấy ra cho heo ở ô chuồng khác ăn</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>Pakan di wadah basah dan jadi lembek. Apa yang harus dilakukan?</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>Buang pakan lama, bersihkan wadah, lalu isi pakan baru</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>Tambah pakan baru di atasnya</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>Biarkan sampai kering</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>Ambil dan berikan ke babi di kandang lain</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>beginner-guide/07_離乳舎.md 4 給餌管理 ステップ4（残餌の除去・清掃）／21_飼料の基礎知識.md 9 残餌は再利用しない</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>すのこの上の丸い金属のえさ皿。中のえさが水でぬれて、どろどろになっている</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>T0196</t>
+        </is>
+      </c>
+      <c r="AL323" t="inlineStr">
+        <is>
+          <t>T0196</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>q323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>videos/q323.mp4</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>離乳して離乳舎に来たばかり（1週間以内）の子豚には、えさをどうあげますか？</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>少しずつ、1日に何回にも分けてあげる</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>1日1回、たくさんまとめてあげる</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2〜3日に1回だけあげる</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>母豚用のえさをあげる</t>
+        </is>
+      </c>
+      <c r="K324" t="n">
+        <v>1</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>離乳した直後（入舎〜7日目）は、消化の負担を減らすため少しずつ1日4〜5回に分けてあげます。「少量ずつ、こまめに」が基本です。</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>How should you feed piglets that were just weaned and moved to the nursery (within 1 week)?</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Give small amounts, several times a day</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Give a lot once a day</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Feed only once every 2–3 days</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Give them sow feed</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>Heo con vừa cai sữa, mới chuyển sang chuồng cai sữa (trong vòng 1 tuần) thì cho ăn thế nào?</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>Cho ăn ít một, chia làm nhiều lần trong ngày</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>Mỗi ngày cho ăn 1 lần thật nhiều</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2–3 ngày mới cho ăn 1 lần</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>Cho ăn cám của heo nái</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>Bagaimana memberi pakan anak babi yang baru disapih dan baru masuk kandang sapih (kurang dari 1 minggu)?</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>Sedikit-sedikit, dibagi beberapa kali sehari</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>Sekali sehari dalam jumlah banyak</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>Hanya sekali tiap 2–3 hari</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>Beri pakan induk</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>beginner-guide/07_離乳舎.md 4 給餌管理 ステップ3（1日の給餌回数）</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>離乳舎の豚房。すのこ床に子豚がたくさんいて、中央に白い給餌器（赤いふた）がある</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>T0801</t>
+        </is>
+      </c>
+      <c r="AL324" t="inlineStr">
+        <is>
+          <t>T0801</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>q324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>videos/q324.mp4</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>離乳したばかりの子豚にあげるえさ（プレスターター）の特徴はどれですか？</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>乳の成分が入っていて、消化しやすい</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>いちばん値段が安い</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>繊維が多く、おなかがいっぱいになりやすい</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>脂肪をつけるための出荷前のえさ</t>
+        </is>
+      </c>
+      <c r="K325" t="n">
+        <v>1</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>離乳直後に使うプレスターターは、乳の成分が入っていて消化しやすく、子豚がよく食べるように作られています。いちばん品質が高く、値段も高いえさです。</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>What is special about the feed for just-weaned piglets (pre-starter)?</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>It contains milk ingredients and is easy to digest</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>It is the cheapest feed</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>It has a lot of fiber to make pigs feel full</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>It is a pre-shipment feed for adding fat</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>Thức ăn cho heo con vừa cai sữa (cám tập ăn) có đặc điểm gì?</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>Có thành phần sữa, dễ tiêu hóa</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Giá rẻ nhất</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Nhiều chất xơ, heo mau no</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>Là cám vỗ béo trước khi xuất chuồng</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>Apa ciri pakan untuk anak babi yang baru disapih (pre-starter)?</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>Mengandung bahan susu dan mudah dicerna</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>Harganya paling murah</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>Banyak serat supaya cepat kenyang</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>Pakan penggemukan sebelum dikirim</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 3.1 子豚用飼料（プレスターター）</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>離乳舎の豚房。青いすのこの上に子豚がたくさんいて、赤いふたの給餌器（ホッパー）が2台ある</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>T1181</t>
+        </is>
+      </c>
+      <c r="AL325" t="inlineStr">
+        <is>
+          <t>T1181</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>q325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>videos/q325.mp4</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>離乳舎で、次にえさをあげる時間になっても、えさ箱にえさが残っていました。正しい対応はどれですか？</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>次のえさを10〜20%減らし、体調の悪い子豚がいないかも確かめる</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>次のえさを2倍に増やす</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>何もしないで、同じ量をあげ続ける</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>残ったえさを新しいえさにまぜて使う</t>
+        </is>
+      </c>
+      <c r="K326" t="n">
+        <v>1</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>次の給餌までえさが残っているのは量が多いサインです。次回を10〜20%減らし、体調の悪い子豚がいないかも確かめます。</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>In the nursery, feed is still left in the feeder when it is time for the next feeding. What is the correct action?</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Reduce the next feeding by 10–20% and also check for sick piglets</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Double the next feeding</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Do nothing and keep giving the same amount</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Mix the leftover feed with new feed</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>Ở chuồng cai sữa, đến giờ cho ăn lần sau mà trong máng vẫn còn thức ăn. Cách xử lý đúng là gì?</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>Giảm lần sau 10–20% và kiểm tra xem có heo con nào không khỏe không</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Tăng gấp đôi lần sau</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Không làm gì, vẫn cho ăn lượng như cũ</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>Trộn thức ăn thừa vào thức ăn mới</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>Di kandang sapih, saat waktunya memberi pakan lagi, pakan di tempat pakan masih tersisa. Tindakan yang benar adalah?</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>Kurangi pakan berikutnya 10–20% dan cek apakah ada anak babi yang sakit</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>Gandakan pakan berikutnya</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>Tidak melakukan apa-apa, tetap beri jumlah yang sama</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>Campur sisa pakan dengan pakan baru</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>beginner-guide/07_離乳舎.md 4 給餌管理 ステップ5（残餌管理）</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>夜の離乳舎の豚房。すのこ床に子豚が多数いて、奥の給餌器のまわりに集まっている</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>T1074@0</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>動画2.7秒</t>
+        </is>
+      </c>
+      <c r="AL326" t="inlineStr">
+        <is>
+          <t>T1074@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>q326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>videos/q326.mp4</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>動画のような肥育舎で、えさを次の種類に切り替えます。正しいやり方はどれですか？</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>5〜7日かけて、古いえさと新しいえさをまぜながら少しずつ変える</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>ある日から全部いっぺんに新しいえさにする</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>1日えさを止めてから新しいえさにする</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>古いえさと新しいえさを1日ごとに交代であげる</t>
+        </is>
+      </c>
+      <c r="K327" t="n">
+        <v>1</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>えさを急に変えると消化不良や下痢になります。肥育舎では5〜7日かけて、古いえさと新しいえさをまぜながら少しずつ切り替えます。</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>In a finishing barn like the one in the video, you are changing to the next type of feed. What is the correct way?</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Change little by little over 5–7 days, mixing old and new feed</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Switch all at once to the new feed one day</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Stop feeding for a day, then give the new feed</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Alternate old and new feed every other day</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>Ở chuồng heo thịt như trong video, cần đổi sang loại cám tiếp theo. Cách làm đúng là gì?</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>Đổi dần trong 5–7 ngày, trộn cám cũ với cám mới</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Đổi hết sang cám mới ngay trong một ngày</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>Ngừng cho ăn 1 ngày rồi mới cho cám mới</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>Ngày cám cũ, ngày cám mới luân phiên</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>Di kandang penggemukan seperti di video, pakan akan diganti ke jenis berikutnya. Cara yang benar adalah?</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Ganti sedikit demi sedikit selama 5–7 hari sambil mencampur pakan lama dan baru</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>Langsung ganti semua ke pakan baru dalam satu hari</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>Hentikan pakan satu hari, lalu beri pakan baru</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>Pakan lama dan baru diberikan bergantian tiap hari</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>beginner-guide/08_肥育舎.md 2 給餌・飼料管理 ステップ2（飼料切り替えの混合スケジュール）</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>おがくず床の豚房。左手前に白い給餌器があり、育成〜肥育豚が歩いている</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>T0897@0</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>動画2.0秒。離乳舎の切り替えは3〜5日（07章）なので、肥育舎と明記した</t>
+        </is>
+      </c>
+      <c r="AL327" t="inlineStr">
+        <is>
+          <t>T0897@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>q327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>videos/q327.mp4</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>豚が水を十分に飲めないと、えさを食べる量はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>へる</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>ふえる</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>変わらない</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>2倍になる</t>
+        </is>
+      </c>
+      <c r="K328" t="n">
+        <v>1</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>「水を飲まなければ、エサも食べない」。飲む水が減ると、えさを食べる量も同じように減ります。</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>If pigs cannot drink enough water, what happens to the amount of feed they eat?</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>It goes down</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>It goes up</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>It stays the same</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>It doubles</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>Nếu heo không được uống đủ nước thì lượng thức ăn heo ăn sẽ thế nào?</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>Giảm xuống</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Tăng lên</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>Không thay đổi</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>Tăng gấp đôi</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>Jika babi tidak bisa minum cukup air, bagaimana jumlah pakan yang dimakannya?</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>Berkurang</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>Bertambah</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>Tetap sama</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>Menjadi dua kali lipat</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 8.1 水は飼料と同じくらい重要</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>おがくず床の豚房。育成豚が給餌器の受け皿に鼻を近づけている</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>T0684</t>
+        </is>
+      </c>
+      <c r="AL328" t="inlineStr">
+        <is>
+          <t>T0684</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>q328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>videos/q328.mp4</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>飼料・栄養</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>肥育豚が、えさを100kg食べて、体重が40kgふえました。飼料要求率（FCR＝食べたえさ÷ふえた体重）はいくつですか？</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="K329" t="n">
+        <v>1</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>FCR＝食べたえさ÷ふえた体重。100kg÷40kg＝2.5です。数字が小さいほど、少ないえさで太れる優秀な豚です。</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>A finishing pig ate 100 kg of feed and gained 40 kg. What is its feed conversion ratio (FCR = feed eaten ÷ weight gained)?</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>Một con heo thịt ăn 100 kg thức ăn và tăng 40 kg. Hệ số chuyển hóa thức ăn (FCR = thức ăn đã ăn ÷ trọng lượng tăng) là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>Seekor babi potong makan 100 kg pakan dan beratnya naik 40 kg. Berapa rasio konversi pakannya (FCR = pakan yang dimakan ÷ pertambahan berat)?</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>beginner-guide/21_飼料の基礎知識.md 7 飼料効率（FCR）</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>土の床の肥育豚房。多数の肥育豚と、右側に金属の給餌器がある</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>T0046</t>
+        </is>
+      </c>
+      <c r="AL329" t="inlineStr">
+        <is>
+          <t>T0046</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>q329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>videos/q329.mp4</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>動画の左上にいる大きな豚は、何をしていますか？</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>えさ箱に頭を入れて、えさを食べている</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>横になって寝ている</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>ほかの豚とけんかしている</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>水をあびている</t>
+        </is>
+      </c>
+      <c r="K330" t="n">
+        <v>1</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>左の豚は、えさ箱に頭を入れてえさを食べています。</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>What is the big pig at the top left of the video doing?</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Eating with its head in the feeder</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Lying down asleep</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>Fighting with another pig</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Taking a shower of water</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>Con heo lớn ở phía trên bên trái trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>Đang chúi đầu vào máng để ăn</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>Đang nằm ngủ</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Đang đánh nhau với con khác</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>Đang tắm nước</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>Apa yang sedang dilakukan babi besar di kiri atas dalam video?</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>Memasukkan kepala ke tempat pakan dan sedang makan</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>Berbaring tidur</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>Berkelahi dengan babi lain</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>Sedang mandi air</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>映像</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>土の床の肥育豚房。左上の豚が、柵ぎわの金属のえさ箱に頭を入れている。左下の豚の背中に赤いスプレーの線がある</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>T0686</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>左側には2頭（左上=えさ箱に頭を入れている／左下=赤い線の豚・頭が写っていない）いて「左の豚」では特定できないため「左上」に直した</t>
+        </is>
+      </c>
+      <c r="AL330" t="inlineStr">
+        <is>
+          <t>T0686</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>q330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>videos/q330.mp4</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>出荷の準備では、出荷する豚の体にスプレーで印をつけます。何のためですか？</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>出荷する豚をまちがえないため</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>豚の体を消毒するため</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>豚をきれいに見せるため</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>豚の体温を下げるため</t>
+        </is>
+      </c>
+      <c r="K331" t="n">
+        <v>1</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>出荷の数日前に、出荷する豚にスプレーで印をつけます。出荷する豚をまちがえないためです。</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>When preparing for shipment, the pigs to be shipped are marked with spray paint. Why?</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>So you do not ship the wrong pigs</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>To disinfect the pigs</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>To make the pigs look nice</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>To cool the pigs down</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>Khi chuẩn bị xuất chuồng, người ta xịt sơn đánh dấu lên heo sẽ xuất. Để làm gì?</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>Để không xuất nhầm heo</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Để sát trùng cho heo</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>Để heo trông đẹp hơn</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>Để hạ nhiệt cho heo</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>Saat persiapan pengiriman, babi yang akan dikirim diberi tanda dengan cat semprot. Untuk apa?</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Supaya tidak salah mengirim babi</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>Untuk mendisinfeksi babi</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>Supaya babi terlihat bagus</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>Untuk menurunkan suhu tubuh babi</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>beginner-guide/08_肥育舎.md 3 出荷管理 ステップ2〜3（マーキング）</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>土の床の肥育豚房。左下の豚の背中に赤いスプレーの線がある</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>T0686</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>写真の赤い線が出荷用の印かは不明。問いは一般論にしてある</t>
+        </is>
+      </c>
+      <c r="AL331" t="inlineStr">
+        <is>
+          <t>T0686</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>q331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>videos/q331.mp4</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>動画の豚房の奥にいる豚たちは、何をしていますか？</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>横になって休んでいる</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>えさを食べている</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>走り回っている</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>トラックに乗っている</t>
+        </is>
+      </c>
+      <c r="K332" t="n">
+        <v>1</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>奥の豚たちは、すのこの上で横になって休んでいます。</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>What are the pigs at the back of the pen in the video doing?</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Lying down and resting</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Eating feed</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Running around</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Getting on a truck</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>Những con heo ở phía trong ô chuồng trong video đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>Đang nằm nghỉ</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Đang ăn</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Đang chạy lung tung</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Đang lên xe tải</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan babi-babi di bagian belakang kandang dalam video?</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>Berbaring beristirahat</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>Sedang makan</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>Berlarian</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>Naik ke truk</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>映像</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>肥育豚舎の豚房を柵の外から見ている。手前に3頭が立ち、奥のぬれた床で多くの豚が横になっている</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>T0749</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>映像どおり（奥の豚は横になっている）。scene の「すのこの上」は実物ではぬれたコンクリート床なので監修用の記述だけ直した</t>
+        </is>
+      </c>
+      <c r="AL332" t="inlineStr">
+        <is>
+          <t>T0749</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>q332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>videos/q332.mp4</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>出荷の前の日、肥育豚に対してすることはどれですか？</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>えさは止めるが、水は止めない</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>水は止めるが、えさはいつもどおりあげる</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>えさも水も止める</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>えさをいつもより多くあげる</t>
+        </is>
+      </c>
+      <c r="K333" t="n">
+        <v>1</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>出荷の前は、えさを止めます（輸送中の嘔吐やよごれを防ぐため）。でも、水は脱水を防ぐため絶対に止めません。</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>On the day before shipment, what do you do for the finishing pigs?</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Stop the feed, but do not stop the water</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Stop the water, but give feed as usual</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Stop both feed and water</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Give more feed than usual</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>Ngày trước khi xuất chuồng, cần làm gì với heo thịt?</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>Ngừng cho ăn nhưng không ngừng nước uống</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Ngừng nước nhưng vẫn cho ăn như thường</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>Ngừng cả thức ăn và nước</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Cho ăn nhiều hơn mọi ngày</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>Sehari sebelum pengiriman, apa yang dilakukan pada babi potong?</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>Pakan dihentikan, tetapi air minum tidak dihentikan</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>Air dihentikan, tetapi pakan diberikan seperti biasa</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>Pakan dan air sama-sama dihentikan</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>Pakan diberikan lebih banyak dari biasa</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md ステップ2 出荷前の絶食／08_肥育舎.md 3 出荷管理 ステップ3</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>肥育豚舎の豚房。出荷が近い大きさの肥育豚がいる</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>T0749</t>
+        </is>
+      </c>
+      <c r="AL333" t="inlineStr">
+        <is>
+          <t>T0749</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>q333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>videos/q333.mp4</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>出荷のとき、えさを止めるのは出荷の何時間前からが目安ですか？</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>12〜18時間前</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>1時間前</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>3日前</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>1週間前</t>
+        </is>
+      </c>
+      <c r="K334" t="n">
+        <v>1</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>出荷の12〜18時間前からえさを止めます（前の日の夕方の給餌を止めるのが基本）。水は止めません。</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>About how many hours before shipment should you stop feeding?</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>12–18 hours before</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>1 hour before</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>3 days before</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>1 week before</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>Khi xuất chuồng, nên ngừng cho ăn trước khoảng bao nhiêu giờ?</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>Trước 12–18 giờ</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Trước 1 giờ</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>Trước 3 ngày</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Trước 1 tuần</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>Saat pengiriman, pakan dihentikan kira-kira berapa jam sebelumnya?</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>12–18 jam sebelumnya</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>1 jam sebelumnya</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>3 hari sebelumnya</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>1 minggu sebelumnya</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md ステップ2 出荷前の絶食</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>開放型の肥育豚舎。豚房に肥育豚がいて、手前に給餌器の一部が見える</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>T0747</t>
+        </is>
+      </c>
+      <c r="AL334" t="inlineStr">
+        <is>
+          <t>T0747</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>q334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>videos/q334.mp4</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>「ロース」「バラ」「モモ」は、何の名前ですか？</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>豚肉の部位（体のどこの肉か）の名前</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>豚の品種の名前</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>えさの種類の名前</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>豚の病気の名前</t>
+        </is>
+      </c>
+      <c r="K335" t="n">
+        <v>1</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>ロース・バラ・モモは、豚肉の部位（体のどの場所の肉か）の名前です。</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>What are "loin," "belly," and "ham"?</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Names of cuts of pork (which part of the body the meat is from)</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Names of pig breeds</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Names of feed types</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Names of pig diseases</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>"Thăn", "ba chỉ", "đùi" là tên của cái gì?</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>Tên các phần thịt heo (thịt ở phần nào của cơ thể)</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>Tên giống heo</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>Tên loại thức ăn</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Tên bệnh của heo</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>"Has (loin)", "samcan (belly)", dan "paha (ham)" adalah nama apa?</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>Nama bagian daging babi (daging dari bagian tubuh mana)</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>Nama ras babi</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>Nama jenis pakan</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>Nama penyakit babi</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md 7 豚肉の主な部位</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>開放型の肥育豚舎。豚房に肥育豚が多数いる（やや暗い）</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>T0021</t>
+        </is>
+      </c>
+      <c r="AL335" t="inlineStr">
+        <is>
+          <t>T0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>q335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>videos/q335.mp4</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>出荷の日、豚をトラックまで連れていくときの正しいやり方はどれですか？</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>静かに、ゆっくり、豚のペースで進ませる</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>大声を出して走らせる</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>棒でたたいて急がせる</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>豚房の豚を全部いっぺんに追い出す</t>
+        </is>
+      </c>
+      <c r="K336" t="n">
+        <v>1</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>出荷の積み込みは「静かに、ゆっくり、豚のペースで」。急かしたり、たたいたり、大声を出したりしません。</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>On shipping day, what is the correct way to move pigs to the truck?</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Move them quietly and slowly, at the pigs' own pace</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Shout and make them run</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>Hit them with a stick to hurry them</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Drive all the pigs out of the pen at once</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>Ngày xuất chuồng, cách lùa heo lên xe tải đúng là gì?</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>Lùa nhẹ nhàng, từ từ, theo tốc độ của heo</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>La to cho heo chạy</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>Dùng gậy đánh cho heo đi nhanh</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Lùa hết heo trong ô ra một lúc</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>Pada hari pengiriman, bagaimana cara yang benar menggiring babi ke truk?</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>Dengan tenang, pelan-pelan, sesuai kecepatan babi</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>Berteriak supaya babi berlari</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>Memukul dengan tongkat supaya cepat</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>Menggiring semua babi di kandang sekaligus</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>beginner-guide/08_肥育舎.md 3 出荷管理 ステップ4（誘導・積み込み）／25_出荷から食卓まで.md ステップ3</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>コンクリート床の豚房で、肥育豚が鼻で床のにおいをかぎながら歩いている</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>T1028@0</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>動画2.8秒。q193（母豚の通路移動）とは場面が別（出荷の積み込み）</t>
+        </is>
+      </c>
+      <c r="AL336" t="inlineStr">
+        <is>
+          <t>T1028@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>q336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>videos/q336.mp4</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>出荷の直前に、豚を追い回したり、暑い所に置いたりすると、肉はどうなりやすいですか？</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>色がうすく、やわらかく、水っぽい肉になる</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>色が赤く、ちょうどよい肉になる</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>脂肪が多い、あまい肉になる</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>肉には何も変わりはない</t>
+        </is>
+      </c>
+      <c r="K337" t="n">
+        <v>1</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>出荷直前に追い回す・たたく・暑い所に置くなどの急なストレスは、色がうすく水っぽい「PSE肉」の原因になります。暗くかたい肉（DFD肉）は長い時間のストレスが原因です。</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>If pigs are chased around or kept in a hot place just before shipment, what tends to happen to the meat?</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>It becomes pale, soft, and watery</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>It becomes nicely red and just right</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>It becomes fatty and sweet</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Nothing changes in the meat</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>Nếu ngay trước khi xuất chuồng mà rượt đuổi heo hoặc để heo ở chỗ nóng thì thịt dễ bị làm sao?</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>Thịt bị nhạt màu, mềm nhũn, rỉ nước</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>Thịt đỏ đẹp, vừa phải</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>Thịt nhiều mỡ, ngọt hơn</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Thịt không thay đổi gì</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>Jika tepat sebelum pengiriman babi dikejar-kejar atau ditaruh di tempat panas, daging cenderung jadi seperti apa?</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Warnanya pucat, lembek, dan berair</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>Warnanya merah bagus dan pas</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>Banyak lemak dan terasa manis</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>Tidak ada perubahan pada daging</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md 4 PSE肉／08_肥育舎.md 3 出荷管理 ステップ5</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>コンクリート床の豚房を上から見ている。肥育豚が横になったり立ったりしている</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>T1027</t>
+        </is>
+      </c>
+      <c r="AL337" t="inlineStr">
+        <is>
+          <t>T1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>q337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>videos/q337.mp4</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>出荷のときに乱暴にあつかって、豚の体にあざができました。肉にはどんな問題がありますか？</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>あざの部分は切りとって捨てるので、とれる肉がへる</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>あざの部分がいちばん高く売れる</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>肉がやわらかくなって、おいしくなる</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>問題はない</t>
+        </is>
+      </c>
+      <c r="K338" t="n">
+        <v>1</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>あざ（打撲）のある部分は切りとって捨てるので、とれる肉がへります。乱暴にあつかったり、せまい通路でぶつけたりしないことが大切です。</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Rough handling during shipment left bruises on a pig. What is the problem for the meat?</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>The bruised parts are cut off and thrown away, so less meat is obtained</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>The bruised parts sell for the highest price</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>The meat becomes softer and tastier</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>There is no problem</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>Khi xuất chuồng, do đối xử thô bạo nên heo bị bầm tím. Thịt sẽ bị vấn đề gì?</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>Phần bị bầm phải cắt bỏ nên lượng thịt thu được giảm</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>Phần bị bầm bán được giá cao nhất</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>Thịt mềm và ngon hơn</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Không có vấn đề gì</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>Karena ditangani dengan kasar saat pengiriman, tubuh babi jadi memar. Apa masalahnya bagi daging?</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>Bagian yang memar dipotong dan dibuang, jadi daging yang didapat berkurang</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>Bagian memar dijual paling mahal</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>Daging jadi lebih empuk dan enak</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>Tidak ada masalah</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md 4 打撲（あざ）</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>土の床の豚房に、大きな肥育豚がたくさんいる</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>T0687</t>
+        </is>
+      </c>
+      <c r="AL338" t="inlineStr">
+        <is>
+          <t>T0687</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>q338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>videos/q338.mp4</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>耳標の番号や出荷の記録を、正しく残しておくのはなぜですか？</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>どこの農場から、いつ出荷された豚か、あとで追えるようにするため</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>豚の体重をふやすため</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>豚を静かにさせるため</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>えさ代を安くするため</t>
+        </is>
+      </c>
+      <c r="K339" t="n">
+        <v>1</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>耳標の番号や出荷の記録があると、「この肉はどこの農場から、いつ出荷された豚か」をあとで追えます（トレーサビリティ）。問題が起きたときに原因をすぐ調べられます。</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Why must ear tag numbers and shipping records be kept correctly?</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>So you can later trace which farm the pig came from and when it was shipped</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>To make pigs gain weight</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>To keep pigs calm</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>To lower feed costs</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>Tại sao phải ghi chép đúng số thẻ tai và hồ sơ xuất chuồng?</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>Để sau này truy được heo từ trại nào, xuất chuồng khi nào</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Để heo tăng cân</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Để heo yên tĩnh</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Để giảm tiền thức ăn</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>Mengapa nomor anting telinga dan catatan pengiriman harus disimpan dengan benar?</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>Supaya nanti bisa dilacak babi dari peternakan mana dan kapan dikirim</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>Supaya berat babi bertambah</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>Supaya babi tenang</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>Supaya biaya pakan lebih murah</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>beginner-guide/25_出荷から食卓まで.md 5 トレーサビリティシステム</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>おがくず床の豚房で、育成〜肥育豚が歩いている</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>T0900</t>
+        </is>
+      </c>
+      <c r="AL339" t="inlineStr">
+        <is>
+          <t>T0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>q339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>videos/q339.mp4</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>肉豚・出荷・肉</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>出荷の直前に、豚が興奮して暴れています。どうしますか？</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>10〜15分待って落ち着かせてから、静かに誘導し直す</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>大声でしかって、すぐに積み込む</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>電気ショッカーをたくさん使って積み込む</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>暴れている豚を棒でたたいておとなしくさせる</t>
+        </is>
+      </c>
+      <c r="K340" t="n">
+        <v>1</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>興奮したまま積み込むとPSE肉のリスクが大きく上がります。10〜15分待って落ち着かせてから、静かに誘導し直します。</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Right before shipment, a pig is excited and struggling. What should you do?</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Wait 10–15 minutes to let it calm down, then guide it again quietly</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Scold it loudly and load it right away</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Use the electric prod many times to load it</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Hit it with a stick to make it quiet</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>Ngay trước khi xuất chuồng, heo bị kích động và vùng vẫy. Phải làm gì?</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>Đợi 10–15 phút cho heo bình tĩnh rồi lùa lại nhẹ nhàng</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>La mắng to rồi đưa lên xe ngay</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>Dùng dùi điện nhiều lần để đưa lên xe</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Dùng gậy đánh cho heo yên</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>Tepat sebelum pengiriman, babi gelisah dan meronta. Apa yang harus dilakukan?</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>Tunggu 10–15 menit sampai tenang, lalu giring lagi dengan tenang</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>Bentak dengan keras lalu langsung naikkan ke truk</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>Pakai alat kejut listrik berkali-kali untuk menaikkan</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>Pukul dengan tongkat supaya diam</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>beginner-guide/08_肥育舎.md 3 出荷管理 よくある質問（興奮して暴れている）</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>開放型の肥育豚舎。豚房に大きな肥育豚がいる</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>T0748</t>
+        </is>
+      </c>
+      <c r="AL340" t="inlineStr">
+        <is>
+          <t>T0748</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>q340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>videos/q340.mp4</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>母豚のそばで寝ている小さな豚は、どれですか？</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>母豚の乳を飲んで育っている子豚（哺乳子豚）</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>母豚からはなれた子豚（離乳子豚）</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>出荷まで育てている豚（肥育豚）</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>種付けに使う雄の豚（種雄豚）</t>
+        </is>
+      </c>
+      <c r="K341" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>分娩舎には母豚と、母豚の乳を飲んで育つ子豚（哺乳子豚）がいます。離乳すると子豚は離乳舎へ移ります。</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>What are the small pigs sleeping next to the sow?</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Piglets that still drink the sow's milk (suckling piglets)</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Piglets already separated from the sow (weaned piglets)</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>Pigs raised until shipping (finishing pigs)</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Male pigs used for breeding (boars)</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>Những con heo nhỏ đang ngủ cạnh heo nái là heo gì?</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>Heo con còn bú sữa mẹ (heo con theo mẹ)</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>Heo con đã tách mẹ (heo cai sữa)</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>Heo nuôi đến khi xuất chuồng (heo thịt)</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Heo đực dùng để phối giống (heo nọc)</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>Babi kecil yang tidur di dekat induk itu babi apa?</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>Anak babi yang masih menyusu induk (anak babi menyusu)</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>Anak babi yang sudah dipisah dari induk (babi sapih)</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>Babi yang dipelihara sampai dijual (babi penggemukan)</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>Babi jantan untuk kawin (pejantan)</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>beginner-guide/00_はじめに.md 分娩舎（いる豚）</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>分娩柵の中で横になった母豚の体の上やそばで、小さな子豚が何頭もかたまって寝ている</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>T0594</t>
+        </is>
+      </c>
+      <c r="AL341" t="inlineStr">
+        <is>
+          <t>T0594</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>q341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>videos/q341.mp4</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>このような子豚を母豚からはなす（離乳する）のは、生まれてからだいたい何日目ですか？</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>21〜28日目</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>3〜5日目</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>60〜70日目</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>150日目ごろ</t>
+        </is>
+      </c>
+      <c r="K342" t="n">
+        <v>1</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>子豚はふつう生まれてから21〜28日目に母豚からはなします（離乳）。そのあと離乳舎へ移ります。</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>About how many days after birth are piglets like these separated from the sow (weaned)?</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Day 21–28</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Day 3–5</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Day 60–70</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Around day 150</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>Heo con như thế này được tách mẹ (cai sữa) vào khoảng ngày thứ mấy sau khi sinh?</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Ngày 21–28</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Ngày 3–5</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>Ngày 60–70</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>Khoảng ngày 150</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>Anak babi seperti ini dipisah dari induk (disapih) kira-kira pada hari ke berapa setelah lahir?</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Hari ke-21–28</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>Hari ke-3–5</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>Hari ke-60–70</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>Sekitar hari ke-150</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>beginner-guide/00_はじめに.md 豚の一生（離乳 生後21〜28日目）</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>分娩柵の中で横になった母豚と、そのそばで寝ている哺乳子豚</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>T0594</t>
+        </is>
+      </c>
+      <c r="AL342" t="inlineStr">
+        <is>
+          <t>T0594</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>q342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>videos/q342.mp4</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>母豚のおなかの乳頭（おっぱい）は、ふつう何個くらいありますか？</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>12〜16個</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>4〜6個</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>8個くらい</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>24〜30個</t>
+        </is>
+      </c>
+      <c r="K343" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>母豚の乳頭はふつう12〜16個あります。子豚が乳をよく飲めるよう、乳頭が硬くなっていないかも毎日見ます。</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>How many teats does a sow usually have?</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>12–16</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>4–6</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>About 8</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>24–30</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>Heo nái thường có bao nhiêu núm vú?</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>12–16 núm</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>4–6 núm</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>Khoảng 8 núm</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>24–30 núm</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>Induk babi biasanya punya berapa puting susu?</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>12–16 buah</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>4–6 buah</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>Sekitar 8 buah</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>24–30 buah</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 5.1 各部位の説明（乳頭 通常12-16個）</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>分娩柵の中で横向きに寝た母豚のおなか。乳頭が1列に並んで見え、そばに子豚がいる</t>
+        </is>
+      </c>
+      <c r="AJ343" t="inlineStr">
+        <is>
+          <t>T0181</t>
+        </is>
+      </c>
+      <c r="AK343" t="inlineStr">
+        <is>
+          <t>実物では乳頭は1列しか見えないため scene を事実どおりに修正（問いは manual の12〜16個で映像に依存しない）</t>
+        </is>
+      </c>
+      <c r="AL343" t="inlineStr">
+        <is>
+          <t>T0181</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>q343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>videos/q343.mp4</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>飼養環境・施設</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>豚が横向きに体を伸ばし、重なり合わずに寝ています。部屋の温度はどう考えますか？</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ちょうどよい</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>寒すぎる</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>暑すぎる</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>空気が汚れている</t>
+        </is>
+      </c>
+      <c r="K344" t="n">
+        <v>1</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>横向きに伸びて、適度にはなれて寝ていれば温度はちょうどよいです。重なり合って寝ていれば寒い、極端にバラバラなら暑いサインです。</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>The pigs are sleeping on their sides, stretched out, not piled up. What does this say about the room temperature?</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>It is about right</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>It is too cold</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>It is too hot</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>The air is dirty</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>Heo nằm nghiêng, duỗi thẳng người, không chồng lên nhau. Nhiệt độ chuồng thế nào?</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>Vừa phải</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Quá lạnh</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>Quá nóng</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>Không khí bị bẩn</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>Babi tidur miring dengan badan terjulur dan tidak bertumpuk. Bagaimana suhu ruangannya?</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>Sudah pas</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>Terlalu dingin</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>Terlalu panas</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>Udaranya kotor</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 4.3 観察のコツ（寝方と温度）</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>すのこ床の豚房で、大きな豚3頭が横向きに体を伸ばして寝ており、1頭が立っている。重なり合っていない</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>T0121</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>scene を実物（寝ている3頭＋立っている1頭）に修正。問いは manual 4.3 の適温サインと一致</t>
+        </is>
+      </c>
+      <c r="AL344" t="inlineStr">
+        <is>
+          <t>T0121</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>q344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>videos/q344.mp4</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>赤茶色（赤褐色）の毛は、どの品種の特徴ですか？</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>デュロック</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>ランドレース</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>大ヨークシャー</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>LW（ランドレースと大ヨークシャーをかけ合わせた豚）</t>
+        </is>
+      </c>
+      <c r="K345" t="n">
+        <v>1</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>赤茶色〜茶色の体の品種はデュロックです。ランドレースと大ヨークシャーは白い豚です。</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Reddish-brown hair is a feature of which breed?</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Duroc</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>Landrace</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Large White (Yorkshire)</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>LW (Landrace × Large White cross)</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>Lông màu nâu đỏ là đặc điểm của giống heo nào?</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Duroc</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Landrace</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Yorkshire (Large White)</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>LW (lai Landrace × Yorkshire)</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>Bulu cokelat kemerahan adalah ciri babi jenis apa?</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>Duroc</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>Landrace</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>Large White (Yorkshire)</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>LW (silangan Landrace × Large White)</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 2.2 各品種の特徴（デュロック 赤褐色）</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>ストールの中の赤茶色（茶色）の毛の豚を、後ろから撮っている（品種は写真だけでは断定できない）</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>T0190</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>毛色だけでこの個体をデュロックと断定できないため、映像の個体でなく「赤褐色=どの品種の特徴か」という manual 2.2 の知識を問う形に作り替え</t>
+        </is>
+      </c>
+      <c r="AL345" t="inlineStr">
+        <is>
+          <t>T0190</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>q345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>videos/q345.mp4</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>三元交配（LWD）で、デュロックはどう使われますか？</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>LWの母豚に最後にかける雄（止め雄）</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>ランドレースとかけ合わせる母豚の母方</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>LW母豚をつくるときの父（雄）</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>肉豚を産む母豚</t>
+        </is>
+      </c>
+      <c r="K346" t="n">
+        <v>1</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>三元交配では、LWの母豚に最後にデュロックの雄をかけて、肉豚（LWD）をつくります。デュロックは「止め雄」です。</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>How is the Duroc used in three-way crossing (LWD)?</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>As the final sire mated to LW sows (terminal boar)</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>As the dam line mated with Landrace</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>As the sire used to produce LW sows</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>As the sow that gives birth to market pigs</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>Trong lai ba máu (LWD), giống Duroc được dùng thế nào?</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>Làm heo đực phối cuối cùng với nái LW (đực cuối)</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Làm dòng mẹ để phối với Landrace</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Làm heo bố để tạo ra nái LW</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Làm heo nái đẻ ra heo thịt</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>Dalam persilangan tiga bangsa (LWD), Duroc dipakai sebagai apa?</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>Pejantan terakhir untuk induk LW (pejantan terminal)</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>Garis induk yang dikawinkan dengan Landrace</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>Pejantan untuk membuat induk LW</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>Induk yang melahirkan babi potong</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 2.1 三元交配 / 2.2 デュロック（止め雄）</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>ストールの中の赤茶色の豚を後ろから撮っている</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>T0190</t>
+        </is>
+      </c>
+      <c r="AL346" t="inlineStr">
+        <is>
+          <t>T0190</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>q346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>videos/q346.mp4</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>動画の大きな豚は、どれですか？</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>子豚を産む母豚</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>出荷前の肥育豚</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>離乳子豚</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>哺乳子豚</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>1</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>おなかに乳房が発達した大きな雌豚は、子豚を産む母豚です。</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>What are the big pigs in the video?</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Sows that give birth to piglets</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Finishing pigs before shipping</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Weaned piglets</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Suckling piglets</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>Những con heo lớn trong video là heo gì?</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>Heo nái đẻ ra heo con</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>Heo thịt sắp xuất chuồng</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>Heo cai sữa</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>Heo con theo mẹ</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>Babi besar di video ini babi apa?</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>Induk babi yang melahirkan anak</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>Babi penggemukan yang siap dijual</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>Babi sapih</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>Anak babi menyusu</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 3.1 成長段階・5.3 オスとメスの見分け方</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>コンクリート床の囲いの中に大きな母豚が何頭かいて、作業者がホースを持って中に立っている。母豚のおなかに乳房が見える</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>T0604@0</t>
+        </is>
+      </c>
+      <c r="AL347" t="inlineStr">
+        <is>
+          <t>T0604@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>q347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>videos/q347.mp4</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>動画の豚が母豚だと分かるのは、体のどこを見ればよいですか？</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>おなかの乳頭（乳房）が大きく発達している</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>耳が立っている</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>体が茶色い</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>しっぽが短い</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>1</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>母豚は乳頭がよく発達しています（ふつう12〜16個）。雄や若い豚では乳頭は小さいです。</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Which body part tells you these pigs are sows?</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>The teats (udder) on the belly are well developed</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>The ears stand up</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>The body is brown</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>The tail is short</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>Nhìn vào đâu để biết đây là heo nái?</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>Núm vú (bầu vú) dưới bụng phát triển to</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Tai dựng đứng</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Thân màu nâu</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>Đuôi ngắn</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>Dari bagian tubuh mana kita tahu babi ini induk?</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>Puting susu (ambing) di perut berkembang besar</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>Telinganya tegak</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>Badannya cokelat</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>Ekornya pendek</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 5.3 オスとメスの見分け方（乳頭）</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>囲いの中の母豚。おなかに乳頭が大きく発達しているのが見える</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>T0604@0</t>
+        </is>
+      </c>
+      <c r="AL348" t="inlineStr">
+        <is>
+          <t>T0604@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>q348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>videos/q348.mp4</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>繁殖・分娩</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>動画の豚舎では、母豚はどのように飼われていますか？</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>何頭かいっしょに1つの豚房で（群飼い）</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>1頭ずつ柵の中で（ストール）</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>子豚といっしょに分娩柵の中で</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>外の運動場に放して</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>1</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>1つの豚房に何頭もまとめて飼う方法を群飼いといいます。1頭ずつ柵に入れる方法はストール飼いです。</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>How are the sows kept in this barn?</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Several together in one pen (group housing)</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>One by one in stalls</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>With piglets in farrowing crates</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Let loose in an outdoor yard</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>Trong chuồng này, heo nái được nuôi thế nào?</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>Nhiều con chung một ô (nuôi nhóm)</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Mỗi con một ô cũi (chuồng cá thể)</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>Cùng heo con trong cũi đẻ</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>Thả ra sân vận động ngoài trời</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>Di kandang ini, induk babi dipelihara dengan cara apa?</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>Beberapa ekor bersama dalam satu pen (kandang kelompok)</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>Satu per satu di dalam stall</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>Bersama anaknya di kandang beranak</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>Dilepas di halaman luar</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>beginner-guide/05_妊娠舎.md 個別飼養と群飼の違い</t>
+        </is>
+      </c>
+      <c r="AI349" t="inlineStr">
+        <is>
+          <t>すのこ床の1つの豚房に母豚が何頭もいっしょに入っていて、作業者が母豚の体に手を当てて動かしている</t>
+        </is>
+      </c>
+      <c r="AJ349" t="inlineStr">
+        <is>
+          <t>T0557@3.5</t>
+        </is>
+      </c>
+      <c r="AL349" t="inlineStr">
+        <is>
+          <t>T0557@3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>q349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>videos/q349.mp4</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>動画の子豚たちは、どんな様子ですか？</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>元気に歩き回っている</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>重なり合ってふるえている</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>横にたおれて動かない</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>口を開けてハアハア息をしている</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>1</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>子豚は四本足でしっかり立って、元気に歩き回っています。正常な様子です。</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>How do the piglets look?</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Walking around actively</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Piled up and shivering</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>Lying on their side, not moving</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Panting with their mouths open</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>Những con heo con này trông thế nào?</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>Đi lại khỏe mạnh</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Nằm chồng lên nhau và run</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>Nằm nghiêng, không cử động</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Há miệng thở hổn hển</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>Bagaimana keadaan anak-anak babi ini?</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>Berjalan ke sana kemari dengan sehat</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>Bertumpuk dan menggigil</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>Terbaring miring, tidak bergerak</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>Terengah-engah dengan mulut terbuka</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 5.2 観察で重要なポイント（行動・姿勢）</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>すのこ床の豚房で、離乳子豚が何頭も歩き回ってにおいをかいでいる（上から撮影）</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>T0462@0</t>
+        </is>
+      </c>
+      <c r="AL350" t="inlineStr">
+        <is>
+          <t>T0462@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>q350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>videos/q350.mp4</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>見回りのとき、元気な豚のサインはどれですか？</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>目が澄んでいて、まわりに反応する</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>鼻がかわいてカサカサしている</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>群れからはなれてじっとしている</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>えさを見ても近づかない</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>1</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>元気な豚は目が澄んでいてまわりに反応し、鼻がしっとりしています。群れからはなれてじっとしているのは異常のサインです。</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>During checks, which is a sign of a healthy pig?</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Clear eyes and reacts to its surroundings</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>Dry, cracked snout</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Stays still away from the group</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Does not come near even when it sees feed</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>Khi đi kiểm tra, dấu hiệu nào cho thấy heo khỏe?</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>Mắt trong, phản ứng với xung quanh</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Mũi khô, nứt nẻ</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>Đứng yên, tách khỏi đàn</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>Thấy cám cũng không lại gần</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>Saat keliling, mana tanda babi yang sehat?</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>Matanya jernih dan bereaksi pada sekitarnya</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>Hidungnya kering pecah-pecah</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>Diam saja memisah dari kelompok</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>Tidak mendekat walau melihat pakan</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 5.2 観察で重要なポイント（目の輝き・鼻の湿り・行動）</t>
+        </is>
+      </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>すのこ床の豚房で離乳子豚が歩き回っている</t>
+        </is>
+      </c>
+      <c r="AJ351" t="inlineStr">
+        <is>
+          <t>T0462@0</t>
+        </is>
+      </c>
+      <c r="AL351" t="inlineStr">
+        <is>
+          <t>T0462@0</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>q351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>videos/q351.mp4</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>動画のような離乳舎の子豚は、体重が何kgくらいになると肥育舎へ移りますか？</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>約30kg</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>約7kg</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>約60kg</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>約115kg</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>1</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>離乳舎では離乳直後から体重約30kgまで育て、そのあと肥育舎へ移します。</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>At about what body weight do nursery piglets like these move to the finishing barn?</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>About 30 kg</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>About 7 kg</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>About 60 kg</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>About 115 kg</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>Heo con ở chuồng cai sữa như thế này được chuyển sang chuồng heo thịt khi nặng khoảng bao nhiêu kg?</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>Khoảng 30 kg</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>Khoảng 7 kg</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>Khoảng 60 kg</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>Khoảng 115 kg</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>Anak babi di kandang sapih seperti ini dipindah ke kandang penggemukan saat beratnya kira-kira berapa kg?</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>Sekitar 30 kg</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>Sekitar 7 kg</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>Sekitar 60 kg</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>Sekitar 115 kg</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>beginner-guide/00_はじめに.md 離乳舎（離乳〜体重約30kg）/ 肥育舎</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>離乳舎の豚房。緑色のすのこ床に離乳子豚がたくさんいて、丸い給餌器がある</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>T1090</t>
+        </is>
+      </c>
+      <c r="AL352" t="inlineStr">
+        <is>
+          <t>T1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>q352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>videos/q352.mp4</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>分娩舎の子豚です。子豚について正しいものはどれですか？</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>生まれたときから毛が生えていて、目も開いている</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>生まれて数日は目が開いていない</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>生まれたときは毛が生えていない</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>生まれたときは歯がない</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>1</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>子豚は生まれたときから毛が生えていて、目も開いています。歯もあります。</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>This is a piglet in the farrowing barn. Which is true about piglets?</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>From birth they have hair and their eyes are open</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Their eyes stay closed for a few days after birth</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>They have no hair at birth</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>They have no teeth at birth</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>Đây là heo con ở chuồng đẻ. Điều nào đúng về heo con?</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>Mới sinh đã có lông và mắt đã mở</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>Mắt nhắm vài ngày sau khi sinh</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>Lúc mới sinh chưa có lông</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Lúc mới sinh chưa có răng</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>Ini anak babi di kandang beranak. Mana yang benar tentang anak babi?</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>Sejak lahir sudah berbulu dan matanya terbuka</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>Matanya tertutup beberapa hari setelah lahir</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>Saat lahir belum berbulu</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>Saat lahir belum punya gigi</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>beginner-guide/01_豚の基礎知識.md 3.1 成長段階の一覧（出生時: 毛が生えている、目は開いている、歯がある）</t>
+        </is>
+      </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>分娩舎で、作業者が小さな子豚を両手で持ち上げている。子豚の毛と開いた目が見える（作業者の顔は写っていない）</t>
+        </is>
+      </c>
+      <c r="AJ353" t="inlineStr">
+        <is>
+          <t>T0068</t>
+        </is>
+      </c>
+      <c r="AK353" t="inlineStr">
+        <is>
+          <t>T0446 は同じ場面の別写真（重複のため不使用）</t>
+        </is>
+      </c>
+      <c r="AL353" t="inlineStr">
+        <is>
+          <t>T0068</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>q353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>videos/q353.mp4</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>飼養環境・施設</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>動画の青い道具は、何をはかる道具ですか？</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>pH（酸性かアルカリ性か）</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>温度</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>豚の体重</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>空気の二酸化炭素</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>1</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>青い道具はpH計で、水などが酸性かアルカリ性かをはかります。飲み水の水質検査にもpHの項目があります。</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>What does the blue tool measure?</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>pH (acidic or alkaline)</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Pig body weight</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Carbon dioxide in the air</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>Dụng cụ màu xanh này dùng để đo gì?</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>Độ pH (chua hay kiềm)</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Nhiệt độ</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>Cân nặng của heo</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Khí CO2 trong không khí</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>Alat biru ini untuk mengukur apa?</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>pH (asam atau basa)</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>Suhu</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>Berat badan babi</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>Karbon dioksida di udara</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>beginner-guide/07_離乳舎.md 水質管理（pH）</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>豚舎の給水器のそばの配管に、「pH」と書かれた青い測定器が置かれ、画面に7.86と出ている</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>T0260</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr">
+        <is>
+          <t>何の液を測っているかは写真から断定できないため、道具の名前だけを問う。T0258/T0264〜T0267は同系の写真</t>
+        </is>
+      </c>
+      <c r="AL354" t="inlineStr">
+        <is>
+          <t>T0260</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>q354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>videos/q354.mp4</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>飼養環境・施設</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>作業場の壁にある赤い箱には、何が入っていますか？</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>消火器</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>救急箱</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>ワクチン</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>電気のブレーカー</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>1</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>赤い箱には消火器が入っています。火事のときにすぐ使えるよう、場所を覚えておきます。</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>What is in the red box on the workshop wall?</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>A fire extinguisher</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>A first-aid kit</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>Vaccines</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>An electrical breaker</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>Trong hộp màu đỏ trên tường phòng làm việc có gì?</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>Bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>Hộp cứu thương</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>Vắc-xin</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Cầu dao điện</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>Apa isi kotak merah di dinding ruang kerja?</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>Alat pemadam kebakaran (APAR)</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>Kotak P3K</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>Vaksin</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>Pemutus listrik (breaker)</t>
+        </is>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>beginner-guide/12_設備・道具ガイド.md 7章（作業台に消火器も常備）/ 15_チェックリスト集.md 消火器</t>
+        </is>
+      </c>
+      <c r="AI355" t="inlineStr">
+        <is>
+          <t>作業場の壁に「消火器」と書かれた赤い箱があり、その横に黄色い作業台と道具がならんでいる</t>
+        </is>
+      </c>
+      <c r="AJ355" t="inlineStr">
+        <is>
+          <t>T1165</t>
+        </is>
+      </c>
+      <c r="AL355" t="inlineStr">
+        <is>
+          <t>T1165</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>q355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>videos/q355.mp4</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>飼養環境・施設</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>消火器の点検で確認することは、どれですか？</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>置いてある場所と使用期限</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>中の粉の色</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>毎日の重さ</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>だれも使えないように鍵がかかっているか</t>
+        </is>
+      </c>
+      <c r="K356" t="n">
+        <v>1</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>消火器は、置いてある場所と使用期限を点検で確認します。</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>What do you check when inspecting a fire extinguisher?</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Where it is placed and its expiry date</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>The color of the powder inside</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>Its weight every day</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>That it is locked so no one can use it</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>Khi kiểm tra bình chữa cháy, cần xem gì?</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>Vị trí đặt và hạn sử dụng</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Màu bột bên trong</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>Cân nặng mỗi ngày</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Có khóa lại để không ai dùng được không</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>Saat memeriksa alat pemadam kebakaran, apa yang dicek?</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>Tempat penyimpanan dan tanggal kedaluwarsanya</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>Warna bubuk di dalamnya</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>Beratnya setiap hari</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>Apakah dikunci supaya tidak ada yang memakai</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>beginner-guide/15_チェックリスト集.md（消火器の設置場所・使用期限を確認した）</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>作業場の壁の消火器の箱</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>T1165</t>
+        </is>
+      </c>
+      <c r="AL356" t="inlineStr">
+        <is>
+          <t>T1165</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>q356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>videos/q356.mp4</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>ストールの上に置いてある銀色のバッグは、何ですか？</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>中の物を冷たいまま運ぶ保冷バッグ</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>ごみを入れる袋</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>豚のえさ入れ</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>作業服を入れる袋</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>1</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>銀色のバッグは保冷バッグです。ワクチンなど冷やしておく物を、冷たいまま豚舎へ運びます。</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>What is the silver bag placed on the stall?</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>A cooler bag to carry things while keeping them cold</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>A garbage bag</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>A feed container for pigs</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>A bag for work clothes</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>Túi màu bạc đặt trên ô chuồng là gì?</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>Túi giữ lạnh để mang đồ mà vẫn giữ lạnh</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Túi đựng rác</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>Đồ đựng cám cho heo</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>Túi đựng quần áo lao động</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>Tas perak yang ditaruh di atas stall itu apa?</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>Tas pendingin untuk membawa barang tetap dingin</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>Kantong sampah</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>Tempat pakan babi</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>Tas pakaian kerja</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>beginner-guide/05_妊娠舎.md ワクチン接種（クーラーボックスで持ち運ぶ）</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>妊娠ストールの柵の上に、銀色の保冷バッグ（ソフトクーラー）が置いてある</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>中身は写っていない。ワクチン・精液など何を運ぶバッグかは監修で確認。問いは『保冷バッグ』までに留めた</t>
+        </is>
+      </c>
+      <c r="AL357" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>q357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>videos/q357.mp4</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ワクチンを保冷バッグやクーラーボックスに入れて運ぶのは、なぜですか？</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>温度が上がると、ワクチンの効き目がなくなるから</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>ビンが重くならないようにするため</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>豚にワクチンを見せないため</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>ワクチンをこおらせるため</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>1</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>ワクチンは温度が上がると効き目がなくなります。冷蔵庫から出したら、使う直前まで保冷して運びます。</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Why are vaccines carried in a cooler bag or cooler box?</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Because vaccines lose their effect if they get warm</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>To keep the bottles from getting heavy</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>So the pigs cannot see the vaccine</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>To freeze the vaccine</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>Tại sao phải để vắc-xin trong túi giữ lạnh hoặc thùng đá khi mang đi?</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>Vì nhiệt độ tăng thì vắc-xin mất tác dụng</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Để chai không bị nặng</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>Để heo không nhìn thấy vắc-xin</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>Để làm đông đá vắc-xin</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>Kenapa vaksin dibawa dalam tas pendingin atau cool box?</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>Karena vaksin tidak manjur lagi kalau suhunya naik</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>Supaya botolnya tidak berat</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>Supaya babi tidak melihat vaksin</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>Untuk membekukan vaksin</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>beginner-guide/06_分娩舎.md ワクチン接種の失敗例（常温で放置→効力消失）/ 05_妊娠舎.md 持ち運び</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>妊娠ストールの上の銀色の保冷バッグ</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+      <c r="AL358" t="inlineStr">
+        <is>
+          <t>T0135</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>q358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>videos/q358.mp4</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>動画では、2つのビンをつないで何をしていますか？</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>ワクチンを溶解液でとかしている</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>消毒液を水でうすめている</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>とった血を検査している</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>古い薬を捨てている</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>1</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>溶解液のビンをワクチンのビンにつないで、ワクチンをとかしています。生ワクチンは使う直前にとかします。</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>What is being done by connecting the two bottles?</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Dissolving a vaccine with its diluent</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Diluting disinfectant with water</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Testing collected blood</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Throwing away old medicine</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>Nối hai chai lại với nhau như vậy là đang làm gì?</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>Pha vắc-xin bằng dung dịch pha</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Pha loãng thuốc sát trùng với nước</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>Xét nghiệm máu đã lấy</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Đổ bỏ thuốc cũ</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>Dua botol disambungkan begini untuk apa?</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>Melarutkan vaksin dengan cairan pelarutnya</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>Mengencerkan disinfektan dengan air</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>Memeriksa darah yang diambil</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>Membuang obat lama</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>beginner-guide/05_妊娠舎.md ワクチン接種の手順（生ワクチンは溶解液を加えてよく混ぜる）</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>台の上で、溶解液の大ビン（50mL）を逆さにし、青い接続具で小ビン（ラベルは「スワイバックC」と読める。中は泡立った薄いピンク色の液）につないでいる。まわりにアルミキャップの小ビンが多数</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>T1104</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>実物でラベル「スワイバックC」と接続具による溶解作業を確認。scene/note を実測に更新（問いは変更なし） / 実物確認: 接続具で溶解液を小ビンへ移す構図＝凍結乾燥ワクチンの溶解。小ビンのラベル「スワイバックC」まで読めるが製品名は問わない</t>
+        </is>
+      </c>
+      <c r="AL359" t="inlineStr">
+        <is>
+          <t>T1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>q359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>videos/q359.mp4</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>衛生・防疫</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>生ワクチンをとかしたら、いつまでに使い切りますか？</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2時間以内</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>その日のうち</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>3日以内</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>1週間以内</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>1</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>生ワクチンは、とかしてから2時間以内に使い切ります。余ったら捨てます。必要な量だけとかします。</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Once a live vaccine is dissolved, by when must it be used up?</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Within 2 hours</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Within the same day</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>Within 3 days</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Within 1 week</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>Sau khi pha vắc-xin sống, phải dùng hết trong thời gian bao lâu?</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>Trong vòng 2 giờ</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Trong ngày hôm đó</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>Trong vòng 3 ngày</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>Trong vòng 1 tuần</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>Setelah vaksin hidup dilarutkan, harus habis dipakai dalam berapa lama?</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>Dalam 2 jam</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>Pada hari itu juga</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>Dalam 3 hari</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>Dalam 1 minggu</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>上級</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>beginner-guide/05_妊娠舎.md 生ワクチンと不活化ワクチンの取り扱いの違い（溶解後2時間以内）</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>ビンをつないでワクチンをとかしている</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>T1104</t>
+        </is>
+      </c>
+      <c r="AL360" t="inlineStr">
+        <is>
+          <t>T1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>q360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>videos/q360.mp4</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>動画では、子豚の口に何をしていますか？</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>とがった歯（犬歯）を切っている</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>口から注射をしている</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>薬を飲ませている</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>体温をはかっている</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>1</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>子豚の口を開けて、とがった歯（犬歯）を切っています（歯切り）。農場によっては、けずる方法もあります。</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>What is being done to the piglet's mouth?</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Clipping its sharp teeth (needle teeth)</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>Giving an injection in the mouth</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>Giving it oral medicine</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Taking its temperature</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>Người ta đang làm gì ở miệng heo con?</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Cắt răng nanh nhọn</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Tiêm vào miệng</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>Cho uống thuốc</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>Đo thân nhiệt</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>Apa yang dilakukan pada mulut anak babi?</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Memotong gigi taringnya yang tajam</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>Menyuntik lewat mulut</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>Memberi obat minum</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>Mengukur suhu tubuh</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>初級</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>beginner-guide/06_分娩舎.md 7. 子豚処置（歯切り）</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>子豚処置台のそばで、作業者がひざの上で生まれて間もない子豚をおさえ、口を開けさせている。手に小さな金属の器具（歯切り器の先端）を持つ（作業者の顔は写っていない・左上の別の人も胴のみ）</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>T1221</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>実物で口を開けさせ金属器具を持つ場面と顔の非写り込みを確認。scene/note を実測に更新（問いは変更なし） / 実物確認: 口を開けさせ金属器具を口元へ運ぶ直前の場面。処置台（鉄剤・スプレー等）と併せ歯切りと判断</t>
+        </is>
+      </c>
+      <c r="AL361" t="inlineStr">
+        <is>
+          <t>T1221</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>q361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>videos/q361.mp4</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>子豚・育成</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>子豚の歯を切るのは、なぜですか？</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>母豚の乳頭や、ほかの子豚をきずつけないため</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>えさを食べやすくするため</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>病気の検査をするため</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>子豚を見分ける印にするため</t>
+        </is>
+      </c>
+      <c r="K362" t="n">
+        <v>1</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>子豚の犬歯はするどく、母豚の乳頭や同じ腹の子豚をきずつけます。それを防ぐために歯を切ります（必要な場合のみ・農場の方針による）。</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Why are piglets' teeth clipped?</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>To stop them hurting the sow's teats and other piglets</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>To make it easier to eat feed</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>To test for disease</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>To use as a mark to tell piglets apart</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>Tại sao phải cắt răng heo con?</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>Để không làm tổn thương vú heo mẹ và heo con khác</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>Để dễ ăn cám hơn</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>Để xét nghiệm bệnh</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>Để làm dấu phân biệt heo con</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>Kenapa gigi anak babi dipotong?</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>Supaya tidak melukai puting induk dan anak babi lain</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>Supaya lebih mudah makan pakan</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>Untuk memeriksa penyakit</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>Sebagai tanda untuk membedakan anak babi</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>中級</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>beginner-guide/06_分娩舎.md 7. 子豚処置（なぜやるのか: 歯切り）</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>子豚の口を開けて歯の処置をしている</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>T1221</t>
+        </is>
+      </c>
+      <c r="AL362" t="inlineStr">
+        <is>
+          <t>T1221</t>
         </is>
       </c>
     </row>
